--- a/algorithms/rl_controller/logs/FSTG_EXCEL_RL_PREMIUM.xlsx
+++ b/algorithms/rl_controller/logs/FSTG_EXCEL_RL_PREMIUM.xlsx
@@ -178,32 +178,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,7 +215,7 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,25 +223,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -815,28 +815,28 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Analyse de Données
+          <t>Algèbre 2
 (CM - Amphi 1)
+Section: GP-GI S2</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(CM - Amphi 2)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Analyse 4
+(CM - Amphi 3)
 Section: MSD S4</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Chimie Organique 2
-(CM - Amphi 2)
-Section: GC S4</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(CM - Amphi 3)
-Section: GI S4</t>
-        </is>
-      </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Métrologie Capteurs
+          <t>Automatique
 (CM - Amphi 4)
 Section: GESE S4</t>
         </is>
@@ -855,58 +855,58 @@
       <c r="Q4" s="9" t="n"/>
       <c r="R4" s="10" t="inlineStr">
         <is>
-          <t>Analyse 2
+          <t>Structure de la matière
 (TD - Salle 23)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 24)
 MSD-GC-GESE S2 - Groupe: 3</t>
         </is>
       </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="T4" s="12" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
+      <c r="T4" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
 (TD - Salle 25)
-GB-GEG S2 - Groupe: 1</t>
+MSD-GC-GESE S2 - Groupe: 5</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr">
         <is>
+          <t>Algèbre 2
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="V4" s="12" t="inlineStr">
+        <is>
+          <t>Éléments de Génie Chimique
+(TD - Salle 27)
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W4" s="13" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 28)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X4" s="14" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
+(TD - Salle 29)
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="Y4" s="15" t="inlineStr">
+        <is>
           <t>Développement Personnel
-(TD - Salle 26)
+(TD - Salle 30)
 GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V4" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 27)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="W4" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="X4" s="10" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 29)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="Y4" s="15" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z4" s="9" t="n"/>
@@ -921,34 +921,28 @@
           <t>10:35</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Thermodynamique Chimique et Cinétique
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Géologie Structurale
 (CM - Amphi 1)
-Section: GC S4</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Géologie Structurale
+Section: GEG S4</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
 (CM - Amphi 2)
-Section: GEG S4</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie
 (CM - Amphi 3)
-Section: GESE S4</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Analyse 4
-(CM - Amphi 4)
-Section: MSD S4</t>
-        </is>
-      </c>
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n"/>
       <c r="H5" s="9" t="n"/>
@@ -961,60 +955,60 @@
       <c r="O5" s="9" t="n"/>
       <c r="P5" s="9" t="n"/>
       <c r="Q5" s="9" t="n"/>
-      <c r="R5" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>Analyse 4
 (TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 24)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
         <is>
           <t>Analyse 2
-(TD - Salle 24)
+(TD - Salle 25)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="U5" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 26)
 GP-GI S2 - Groupe: 6</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="U5" s="11" t="inlineStr">
-        <is>
-          <t>Biologie Moléculaire et Génétique
-(TD - Salle 26)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V5" s="14" t="inlineStr">
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
-(TD - Salle 27)
+(TD - Salle 28)
 GP-GI S2 - Groupe: 5</t>
         </is>
       </c>
-      <c r="W5" s="12" t="inlineStr">
+      <c r="X5" s="5" t="inlineStr">
         <is>
           <t>Biologie Animale et Végétale
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="X5" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
 (TD - Salle 29)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="Y5" s="5" t="inlineStr">
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="Y5" s="15" t="inlineStr">
         <is>
           <t>Développement Personnel
 (TD - Salle 30)
-GP S4 - Groupe: 1</t>
+GI S4 - Groupe: 2</t>
         </is>
       </c>
       <c r="Z5" s="9" t="n"/>
@@ -1030,7 +1024,13 @@
         </is>
       </c>
       <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
+Section: GP S4</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="9" t="n"/>
@@ -1045,50 +1045,14 @@
       <c r="O6" s="9" t="n"/>
       <c r="P6" s="9" t="n"/>
       <c r="Q6" s="9" t="n"/>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 23)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S6" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 24)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="T6" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="U6" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="R6" s="9" t="n"/>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="9" t="n"/>
+      <c r="U6" s="9" t="n"/>
       <c r="V6" s="9" t="n"/>
-      <c r="W6" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="W6" s="9" t="n"/>
       <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="Y6" s="9" t="n"/>
       <c r="Z6" s="9" t="n"/>
       <c r="AA6" s="9" t="n"/>
       <c r="AB6" s="9" t="n"/>
@@ -1101,26 +1065,32 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (CM - Amphi 1)
+Section: GP-GI S2</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(CM - Amphi 2)
 Section: MSD S4</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 2)
-Section: GEG S4</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Analyse 4
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Electrotechnique
+(CM - Amphi 3)
+Section: GESE S4</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Chimie Minérale 2
 (CM - Amphi 4)
-Section: GP S4</t>
+Section: GC S4</t>
         </is>
       </c>
       <c r="F7" s="9" t="n"/>
@@ -1135,60 +1105,60 @@
       <c r="O7" s="9" t="n"/>
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
+      <c r="R7" s="13" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 23)
 GI S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
+(TD - Salle 26)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V7" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
         <is>
           <t>Analyse 2
-(TD - Salle 24)
+(TD - Salle 28)
 MSD-GC-GESE S2 - Groupe: 1</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 25)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="U7" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 26)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V7" s="11" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 27)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="W7" s="10" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="X7" s="10" t="inlineStr">
-        <is>
-          <t>Analyse 2
+      <c r="X7" s="11" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
 (TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="Y7" s="5" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="Y7" s="10" t="inlineStr">
+        <is>
+          <t>Physiologie Animale et Végétale
 (TD - Salle 30)
-GB-GEG S2 - Groupe: 5</t>
+GB S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z7" s="9" t="n"/>
@@ -1203,22 +1173,22 @@
           <t>16:35</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
 (CM - Amphi 1)
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(CM - Amphi 4)
 Section: GP-GI S2</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(CM - Amphi 2)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n"/>
       <c r="H8" s="9" t="n"/>
@@ -1231,60 +1201,60 @@
       <c r="O8" s="9" t="n"/>
       <c r="P8" s="9" t="n"/>
       <c r="Q8" s="9" t="n"/>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique
 (TD - Salle 23)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S8" s="11" t="inlineStr">
-        <is>
-          <t>Bases de Données
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S8" s="13" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
 (TD - Salle 24)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (TD - Salle 25)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>Structure des Données
 (TD - Salle 26)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V8" s="12" t="inlineStr">
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr">
         <is>
           <t>Géodynamique externe
 (TD - Salle 27)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="W8" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="W8" s="13" t="inlineStr">
+        <is>
+          <t>Analyse de Données
 (TD - Salle 28)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="X8" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X8" s="14" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
 (TD - Salle 29)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="Y8" s="15" t="inlineStr">
-        <is>
-          <t>Pétrographie et Minéralogie
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="Y8" s="10" t="inlineStr">
+        <is>
+          <t>Inférence Statistique et Applications
 (TD - Salle 30)
-GEG S4 - Groupe: 1</t>
+MSD S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z8" s="9" t="n"/>
@@ -1306,28 +1276,22 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Electricité
 (CM - Amphi 2)
+Section: GP-GI S2</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Physiologie Animale et Végétale
+(CM - Amphi 3)
 Section: GB S4</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Optique Physique
-(CM - Amphi 4)
-Section: GP S4</t>
-        </is>
-      </c>
+      <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="9" t="n"/>
@@ -1340,60 +1304,60 @@
       <c r="O10" s="9" t="n"/>
       <c r="P10" s="9" t="n"/>
       <c r="Q10" s="9" t="n"/>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="R10" s="12" t="inlineStr">
+        <is>
+          <t>Chimie Organique 2
 (TD - Salle 23)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="S10" s="11" t="inlineStr">
-        <is>
-          <t>Bases de Données
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 24)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="T10" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="T10" s="12" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
 (TD - Salle 25)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 27)
 GB-GEG S2 - Groupe: 1</t>
         </is>
       </c>
-      <c r="U10" s="14" t="inlineStr">
-        <is>
-          <t>Géomatique
-(TD - Salle 26)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V10" s="12" t="inlineStr">
-        <is>
-          <t>Electrotechnique
-(TD - Salle 27)
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="X10" s="5" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="Y10" s="15" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 30)
 GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W10" s="12" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="X10" s="6" t="inlineStr">
-        <is>
-          <t>Chimie Organique 2
-(TD - Salle 29)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y10" s="8" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
-(TD - Salle 30)
-GI S4 - Groupe: 3</t>
         </is>
       </c>
       <c r="Z10" s="9" t="n"/>
@@ -1408,30 +1372,30 @@
           <t>10:35</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Structure de la matière
 (CM - Amphi 1)
 Section: GP-GI S2</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
 (CM - Amphi 2)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Automatique
+Section: GESE S4</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Analyse de Données
 (CM - Amphi 3)
-Section: GESE S4</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Éléments de Génie Chimique
+Section: MSD S4</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique Chimique et Cinétique
 (CM - Amphi 4)
 Section: GC S4</t>
         </is>
@@ -1448,60 +1412,60 @@
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
-      <c r="R11" s="5" t="inlineStr">
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="U11" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="V11" s="6" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="W11" s="13" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 28)
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X11" s="11" t="inlineStr">
         <is>
           <t>Réactivité Chimique
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="S11" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="T11" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="U11" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
+(TD - Salle 29)
 GB-GEG S2 - Groupe: 1</t>
         </is>
       </c>
-      <c r="V11" s="13" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 27)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="W11" s="10" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="X11" s="10" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="Y11" s="7" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
+          <t>Bases de Données
 (TD - Salle 30)
-GI S4 - Groupe: 3</t>
+GB-GEG S2 - Groupe: 3</t>
         </is>
       </c>
       <c r="Z11" s="9" t="n"/>
@@ -1516,20 +1480,8 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(CM - Amphi 1)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(CM - Amphi 2)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
@@ -1544,43 +1496,37 @@
       <c r="O12" s="9" t="n"/>
       <c r="P12" s="9" t="n"/>
       <c r="Q12" s="9" t="n"/>
-      <c r="R12" s="9" t="n"/>
-      <c r="S12" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 24)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>Analyse 4
+(TD - Salle 23)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="n"/>
+      <c r="T12" s="12" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
 (TD - Salle 25)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 26)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V12" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="U12" s="9" t="n"/>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>Structure des Données
 (TD - Salle 27)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W12" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="X12" s="9" t="n"/>
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="W12" s="9" t="n"/>
+      <c r="X12" s="6" t="inlineStr">
+        <is>
+          <t>Programmation Web
+(TD - Salle 29)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="Y12" s="9" t="n"/>
       <c r="Z12" s="9" t="n"/>
       <c r="AA12" s="9" t="n"/>
@@ -1594,27 +1540,15 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(CM - Amphi 1)
-Section: GC S4</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Structure des Données
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (CM - Amphi 2)
-Section: GESE S4</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Biologie Moléculaire et Génétique
-(CM - Amphi 3)
-Section: GB S4</t>
-        </is>
-      </c>
+Section: GP-GI S2</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n"/>
@@ -1628,60 +1562,60 @@
       <c r="O13" s="9" t="n"/>
       <c r="P13" s="9" t="n"/>
       <c r="Q13" s="9" t="n"/>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
 (TD - Salle 23)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="S13" s="8" t="inlineStr">
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>Algèbre 2
-(TD - Salle 24)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="T13" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
 (TD - Salle 25)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="U13" s="15" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 26)
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="W13" s="12" t="inlineStr">
         <is>
           <t>Analyse Numérique
-(TD - Salle 26)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="V13" s="11" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 27)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W13" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
 (TD - Salle 28)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="X13" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X13" s="11" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
 (TD - Salle 29)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y13" s="11" t="inlineStr">
-        <is>
-          <t>Structure des Données
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="Y13" s="5" t="inlineStr">
+        <is>
+          <t>Bases de Données
 (TD - Salle 30)
-GP S4 - Groupe: 1</t>
+GB-GEG S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="Z13" s="9" t="n"/>
@@ -1697,15 +1631,21 @@
         </is>
       </c>
       <c r="B14" s="9" t="n"/>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
 (CM - Amphi 2)
+Section: MSD S4</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(CM - Amphi 4)
 Section: GB-GEG S2</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n"/>
       <c r="H14" s="9" t="n"/>
@@ -1718,60 +1658,54 @@
       <c r="O14" s="9" t="n"/>
       <c r="P14" s="9" t="n"/>
       <c r="Q14" s="9" t="n"/>
-      <c r="R14" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
+      <c r="R14" s="13" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 23)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="T14" s="14" t="inlineStr">
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="n"/>
+      <c r="T14" s="11" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
 (TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="U14" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 26)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="V14" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 28)
 MSD-GC-GESE S2 - Groupe: 1</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
+      <c r="X14" s="15" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 29)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="Y14" s="13" t="inlineStr">
         <is>
           <t>LTC2 Français
-(TD - Salle 26)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V14" s="10" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="W14" s="15" t="inlineStr">
-        <is>
-          <t>Chimie Minérale 2
-(TD - Salle 28)
+(TD - Salle 30)
 GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="X14" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 29)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="Y14" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 30)
-GP-GI S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="Z14" s="9" t="n"/>
@@ -1793,14 +1727,32 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Recherche Opérationnelle
+(CM - Amphi 1)
+Section: GI S4</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Métrologie Capteurs
+(CM - Amphi 2)
+Section: GESE S4</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Analyse 4
+(CM - Amphi 3)
+Section: GP S4</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Chimie Organique 2
 (CM - Amphi 4)
-Section: GI S4</t>
+Section: GC S4</t>
         </is>
       </c>
       <c r="F16" s="9" t="n"/>
@@ -1815,60 +1767,60 @@
       <c r="O16" s="9" t="n"/>
       <c r="P16" s="9" t="n"/>
       <c r="Q16" s="9" t="n"/>
-      <c r="R16" s="15" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
 (TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="S16" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>Bases de Données
 (TD - Salle 24)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="U16" s="15" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 26)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W16" s="6" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 28)
 GP-GI S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="T16" s="12" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="U16" s="12" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="V16" s="10" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="X16" s="13" t="inlineStr">
+      <c r="X16" s="7" t="inlineStr">
         <is>
           <t>Culture digitale
 (TD - Salle 29)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="Y16" s="15" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
 (TD - Salle 30)
-MSD S4 - Groupe: 1</t>
+MSD-GC-GESE S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z16" s="9" t="n"/>
@@ -1883,28 +1835,16 @@
           <t>10:35</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(CM - Amphi 1)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(CM - Amphi 2)
-Section: GP-GI S2</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Inférence Statistique et Applications
-(CM - Amphi 3)
-Section: MSD S4</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(CM - Amphi 4)
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n"/>
       <c r="H17" s="9" t="n"/>
@@ -1917,60 +1857,60 @@
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="15" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="S17" s="13" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
 (TD - Salle 24)
 GB-GEG S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
 (TD - Salle 25)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="V17" s="12" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
 (TD - Salle 27)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="W17" s="10" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="W17" s="12" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
 (TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 5</t>
+GI S4 - Groupe: 2</t>
         </is>
       </c>
       <c r="X17" s="6" t="inlineStr">
         <is>
-          <t>Structure de la matière
+          <t>Programmation Web
 (TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="Y17" s="5" t="inlineStr">
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="Y17" s="15" t="inlineStr">
         <is>
           <t>Développement Personnel
 (TD - Salle 30)
-GC S4 - Groupe: 1</t>
+GI S4 - Groupe: 3</t>
         </is>
       </c>
       <c r="Z17" s="9" t="n"/>
@@ -1988,9 +1928,9 @@
       <c r="B18" s="9" t="n"/>
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="9" t="n"/>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
 (CM - Amphi 4)
 Section: GB-GEG S2</t>
         </is>
@@ -2007,38 +1947,32 @@
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="9" t="n"/>
       <c r="Q18" s="9" t="n"/>
-      <c r="R18" s="13" t="inlineStr">
-        <is>
-          <t>Analyse 4
-(TD - Salle 23)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S18" s="9" t="n"/>
-      <c r="T18" s="9" t="n"/>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 24)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="T18" s="14" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 25)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="U18" s="9" t="n"/>
-      <c r="V18" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="V18" s="9" t="n"/>
       <c r="W18" s="9" t="n"/>
-      <c r="X18" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
+      <c r="X18" s="5" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="Y18" s="15" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="Y18" s="9" t="n"/>
       <c r="Z18" s="9" t="n"/>
       <c r="AA18" s="9" t="n"/>
       <c r="AB18" s="9" t="n"/>
@@ -2051,22 +1985,28 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(CM - Amphi 4)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
+Section: GEG S4</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Éléments de Génie Chimique
+(CM - Amphi 2)
+Section: GC S4</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(CM - Amphi 3)
+Section: GESE S4</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
       <c r="H19" s="9" t="n"/>
@@ -2079,60 +2019,60 @@
       <c r="O19" s="9" t="n"/>
       <c r="P19" s="9" t="n"/>
       <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="13" t="inlineStr">
-        <is>
-          <t>Analyse 4
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
 (TD - Salle 23)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S19" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 24)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="T19" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 25)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="U19" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="U19" s="15" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (TD - Salle 26)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="V19" s="11" t="inlineStr">
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
         <is>
           <t>Structure des Données
 (TD - Salle 27)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>Programmation Web
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 28)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="X19" s="6" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="X19" s="15" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
 (TD - Salle 29)
-GB S4 - Groupe: 1</t>
+GP-GI S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="Y19" s="6" t="inlineStr">
         <is>
-          <t>Structure de la matière
+          <t>Analyse 2
 (TD - Salle 30)
-GP-GI S2 - Groupe: 6</t>
+MSD-GC-GESE S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="Z19" s="9" t="n"/>
@@ -2147,15 +2087,21 @@
           <t>16:35</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
 (CM - Amphi 1)
 Section: GB-GEG S2</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(CM - Amphi 3)
+Section: GC S4</t>
+        </is>
+      </c>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="9" t="n"/>
       <c r="G20" s="9" t="n"/>
@@ -2169,60 +2115,60 @@
       <c r="O20" s="9" t="n"/>
       <c r="P20" s="9" t="n"/>
       <c r="Q20" s="9" t="n"/>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+      <c r="R20" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
 (TD - Salle 23)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S20" s="14" t="inlineStr">
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T20" s="14" t="inlineStr">
         <is>
           <t>Electricité
-(TD - Salle 24)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="T20" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
 (TD - Salle 25)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 26)
 MSD-GC-GESE S2 - Groupe: 3</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>Physiologie Animale et Végétale
-(TD - Salle 26)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V20" s="7" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 27)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W20" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="W20" s="10" t="inlineStr">
+        <is>
+          <t>Pétrographie et Minéralogie
 (TD - Salle 28)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="X20" s="6" t="inlineStr">
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X20" s="13" t="inlineStr">
         <is>
           <t>LTC2 Français
 (TD - Salle 29)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="Y20" s="13" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 2</t>
+GI S4 - Groupe: 3</t>
         </is>
       </c>
       <c r="Z20" s="9" t="n"/>
@@ -2244,21 +2190,21 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
-Section: GP S4</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Physiologie Animale et Végétale
-(CM - Amphi 3)
-Section: GB S4</t>
-        </is>
-      </c>
+Section: GI S4</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(CM - Amphi 2)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
       <c r="G22" s="9" t="n"/>
@@ -2272,60 +2218,60 @@
       <c r="O22" s="9" t="n"/>
       <c r="P22" s="9" t="n"/>
       <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
+      <c r="R22" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
 (TD - Salle 23)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="S22" s="8" t="inlineStr">
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 24)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="T22" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 25)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
         <is>
           <t>Algèbre 2
-(TD - Salle 24)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(TD - Salle 25)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="U22" s="10" t="inlineStr">
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="V22" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 28)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="X22" s="15" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 29)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="Y22" s="6" t="inlineStr">
         <is>
           <t>Analyse 2
-(TD - Salle 26)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="V22" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 27)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="W22" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 28)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="X22" s="12" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="Y22" s="5" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
 (TD - Salle 30)
-GB-GEG S2 - Groupe: 1</t>
+MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="Z22" s="9" t="n"/>
@@ -2340,22 +2286,28 @@
           <t>10:35</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Structure des Données
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(CM - Amphi 1)
+Section: GP S4</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (CM - Amphi 2)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Programmation Web
+(CM - Amphi 3)
 Section: GI S4</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(CM - Amphi 4)
-Section: GP S4</t>
-        </is>
-      </c>
+      <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
@@ -2368,60 +2320,60 @@
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
 (TD - Salle 23)
-GB-GEG S2 - Groupe: 6</t>
+GB-GEG S2 - Groupe: 3</t>
         </is>
       </c>
       <c r="S23" s="13" t="inlineStr">
         <is>
+          <t>Systèmes d'Information et Bases de Données
+(TD - Salle 24)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T23" s="15" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 25)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 26)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 27)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
           <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="T23" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="U23" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="X23" s="5" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 29)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="Y23" s="6" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 30)
 MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 27)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="X23" s="15" t="inlineStr">
-        <is>
-          <t>Géologie Structurale
-(TD - Salle 29)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y23" s="5" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(TD - Salle 30)
-GB S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z23" s="9" t="n"/>
@@ -2436,20 +2388,14 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Analyse de Données
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (CM - Amphi 1)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(CM - Amphi 2)
-Section: GP-GI S2</t>
-        </is>
-      </c>
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
@@ -2464,48 +2410,30 @@
       <c r="O24" s="9" t="n"/>
       <c r="P24" s="9" t="n"/>
       <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="15" t="inlineStr">
+      <c r="R24" s="9" t="n"/>
+      <c r="S24" s="11" t="inlineStr">
         <is>
           <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 23)
+(TD - Salle 24)
 MSD-GC-GESE S2 - Groupe: 2</t>
         </is>
       </c>
-      <c r="S24" s="9" t="n"/>
-      <c r="T24" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="T24" s="9" t="n"/>
       <c r="U24" s="9" t="n"/>
-      <c r="V24" s="10" t="inlineStr">
+      <c r="V24" s="9" t="n"/>
+      <c r="W24" s="15" t="inlineStr">
         <is>
           <t>Mecanique du point / Optique
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="W24" s="6" t="inlineStr">
-        <is>
-          <t>LTC2 Français
 (TD - Salle 28)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="X24" s="10" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 29)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="X24" s="9" t="n"/>
+      <c r="Y24" s="15" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 30)
 MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
-(TD - Salle 30)
-GI S4 - Groupe: 2</t>
         </is>
       </c>
       <c r="Z24" s="9" t="n"/>
@@ -2520,23 +2448,17 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (CM - Amphi 1)
 Section: MSD-GC-GESE S2</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Structure des Données
-(CM - Amphi 2)
-Section: GP S4</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Programmation Web
 (CM - Amphi 3)
 Section: GI S4</t>
         </is>
@@ -2554,58 +2476,58 @@
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="14" t="inlineStr">
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie
+(TD - Salle 23)
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>Optique Physique
+(TD - Salle 26)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V25" s="11" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
-(TD - Salle 23)
+(TD - Salle 27)
 GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
-      <c r="S25" s="13" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="T25" s="12" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 25)
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
 GB-GEG S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="U25" s="6" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 26)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V25" s="11" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 27)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W25" s="10" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 28)
+      <c r="X25" s="14" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 29)
 GP-GI S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t>Métrologie Capteurs
-(TD - Salle 29)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y25" s="5" t="inlineStr">
-        <is>
-          <t>Analyse de Données
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>Chimie Minérale 2
 (TD - Salle 30)
 GC S4 - Groupe: 1</t>
         </is>
@@ -2624,19 +2546,19 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Mecanique du point / Optique
+          <t>Structure de la matière
 (CM - Amphi 1)
 Section: MSD-GC-GESE S2</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(CM - Amphi 2)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(CM - Amphi 3)
+Section: GB S4</t>
+        </is>
+      </c>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="9" t="n"/>
       <c r="G26" s="9" t="n"/>
@@ -2650,60 +2572,60 @@
       <c r="O26" s="9" t="n"/>
       <c r="P26" s="9" t="n"/>
       <c r="Q26" s="9" t="n"/>
-      <c r="R26" s="13" t="inlineStr">
+      <c r="R26" s="15" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S26" s="13" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
+(TD - Salle 24)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="T26" s="12" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 25)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="U26" s="14" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 26)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
         <is>
           <t>Culture digitale
-(TD - Salle 23)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>Optique Physique
-(TD - Salle 24)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="T26" s="11" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 25)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="U26" s="10" t="inlineStr">
+(TD - Salle 27)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="W26" s="13" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 28)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X26" s="14" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
+(TD - Salle 29)
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="Y26" s="11" t="inlineStr">
         <is>
           <t>Thermodynamique Chimique et Cinétique
-(TD - Salle 26)
+(TD - Salle 30)
 GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V26" s="11" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
-(TD - Salle 27)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="X26" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 29)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="Y26" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 30)
-GP-GI S2 - Groupe: 3</t>
         </is>
       </c>
       <c r="Z26" s="9" t="n"/>
@@ -2725,22 +2647,28 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Chimie Minérale 2
-(CM - Amphi 1)
-Section: GC S4</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(CM - Amphi 2)
+Section: GI S4</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique
+(CM - Amphi 3)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>Pétrographie et Minéralogie
-(CM - Amphi 2)
+(CM - Amphi 4)
 Section: GEG S4</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
       <c r="F28" s="9" t="n"/>
       <c r="G28" s="9" t="n"/>
       <c r="H28" s="9" t="n"/>
@@ -2753,60 +2681,60 @@
       <c r="O28" s="9" t="n"/>
       <c r="P28" s="9" t="n"/>
       <c r="Q28" s="9" t="n"/>
-      <c r="R28" s="10" t="inlineStr">
-        <is>
-          <t>Analyse 2
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
 (TD - Salle 23)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="S28" s="13" t="inlineStr">
+        <is>
+          <t>Métrologie Capteurs
+(TD - Salle 24)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T28" s="15" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 25)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
 GP-GI S2 - Groupe: 1</t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t>Programmation Web
-(TD - Salle 24)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(TD - Salle 25)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="U28" s="12" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V28" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 27)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="W28" s="6" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="W28" s="5" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (TD - Salle 28)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="X28" s="10" t="inlineStr">
-        <is>
-          <t>Analyse 2
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="X28" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 29)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="Y28" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="Y28" s="15" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
 (TD - Salle 30)
-GESE S4 - Groupe: 1</t>
+MSD-GC-GESE S2 - Groupe: 5</t>
         </is>
       </c>
       <c r="Z28" s="9" t="n"/>
@@ -2821,26 +2749,26 @@
           <t>10:35</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(CM - Amphi 1)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (CM - Amphi 2)
-Section: GI S4</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Biochimie Métabolique et Enzymologie
-(CM - Amphi 3)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Géomatique
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Optique Physique
 (CM - Amphi 4)
-Section: GEG S4</t>
+Section: GP S4</t>
         </is>
       </c>
       <c r="F29" s="9" t="n"/>
@@ -2855,60 +2783,60 @@
       <c r="O29" s="9" t="n"/>
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
-      <c r="R29" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
+      <c r="R29" s="15" t="inlineStr">
+        <is>
+          <t>Géologie Structurale
 (TD - Salle 23)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="S29" s="13" t="inlineStr">
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>Culture digitale
 (TD - Salle 24)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 25)
 GP-GI S2 - Groupe: 1</t>
         </is>
       </c>
-      <c r="T29" s="13" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 25)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="U29" s="13" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
 (TD - Salle 26)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V29" s="6" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 27)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="W29" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="W29" s="6" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="X29" s="13" t="inlineStr">
-        <is>
-          <t>Culture digitale
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="X29" s="6" t="inlineStr">
+        <is>
+          <t>Programmation Web
 (TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 3</t>
+GI S4 - Groupe: 3</t>
         </is>
       </c>
       <c r="Y29" s="15" t="inlineStr">
         <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
+          <t>Développement Personnel
 (TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 4</t>
+MSD S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z29" s="9" t="n"/>
@@ -2923,18 +2851,18 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Electricité
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (CM - Amphi 1)
-Section: GP-GI S2</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Analyse 2
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
 (CM - Amphi 2)
-Section: MSD-GC-GESE S2</t>
+Section: GB S4</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -2951,60 +2879,36 @@
       <c r="O30" s="9" t="n"/>
       <c r="P30" s="9" t="n"/>
       <c r="Q30" s="9" t="n"/>
-      <c r="R30" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
 (TD - Salle 23)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="S30" s="13" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 24)
 GP S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="T30" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="U30" s="7" t="inlineStr">
+      <c r="S30" s="9" t="n"/>
+      <c r="T30" s="9" t="n"/>
+      <c r="U30" s="9" t="n"/>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(TD - Salle 27)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="W30" s="12" t="inlineStr">
         <is>
           <t>Analyse Numérique
-(TD - Salle 26)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="V30" s="12" t="inlineStr">
-        <is>
-          <t>Inférence Statistique et Applications
-(TD - Salle 27)
+(TD - Salle 28)
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="X30" s="9" t="n"/>
+      <c r="Y30" s="13" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 30)
 MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="X30" s="5" t="inlineStr">
-        <is>
-          <t>Éléments de Génie Chimique
-(TD - Salle 29)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="Y30" s="13" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 30)
-GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="Z30" s="9" t="n"/>
@@ -3019,28 +2923,22 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>Electrotechnique
-(CM - Amphi 1)
-Section: GESE S4</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(CM - Amphi 2)
-Section: GP-GI S2</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Structure des Données
 (CM - Amphi 3)
-Section: MSD S4</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="n"/>
+Section: GP S4</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Géomatique
+(CM - Amphi 4)
+Section: GEG S4</t>
+        </is>
+      </c>
       <c r="F31" s="9" t="n"/>
       <c r="G31" s="9" t="n"/>
       <c r="H31" s="9" t="n"/>
@@ -3053,60 +2951,60 @@
       <c r="O31" s="9" t="n"/>
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
 (TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S31" s="12" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
 (TD - Salle 24)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="T31" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="U31" s="14" t="inlineStr">
-        <is>
-          <t>Biochimie Métabolique et Enzymologie
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="U31" s="15" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (TD - Salle 26)
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="W31" s="15" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="X31" s="13" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 29)
 GB S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t>Programmation Web
-(TD - Salle 28)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="X31" s="12" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="Y31" s="8" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
+      <c r="Y31" s="5" t="inlineStr">
+        <is>
+          <t>Bases de Données
 (TD - Salle 30)
-GI S4 - Groupe: 1</t>
+GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="Z31" s="9" t="n"/>
@@ -3122,7 +3020,7 @@
         </is>
       </c>
       <c r="B32" s="9" t="n"/>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>Circuits électriques et électronique
 (CM - Amphi 2)
@@ -3130,11 +3028,11 @@
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Inférence Statistique et Applications
 (CM - Amphi 4)
-Section: GB-GEG S2</t>
+Section: MSD S4</t>
         </is>
       </c>
       <c r="F32" s="9" t="n"/>
@@ -3149,60 +3047,60 @@
       <c r="O32" s="9" t="n"/>
       <c r="P32" s="9" t="n"/>
       <c r="Q32" s="9" t="n"/>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>Géomatique
 (TD - Salle 23)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S32" s="13" t="inlineStr">
         <is>
           <t>Systèmes d'Information et Bases de Données
 (TD - Salle 24)
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(TD - Salle 26)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="V32" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X32" s="5" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="Y32" s="13" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 30)
 GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="T32" s="14" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 26)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="V32" s="11" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
-(TD - Salle 27)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="W32" s="10" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="X32" s="6" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="Y32" s="10" t="inlineStr">
-        <is>
-          <t>Automatique
-(TD - Salle 30)
-GESE S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="Z32" s="9" t="n"/>
@@ -3240,14 +3138,62 @@
       <c r="O34" s="9" t="n"/>
       <c r="P34" s="9" t="n"/>
       <c r="Q34" s="9" t="n"/>
-      <c r="R34" s="9" t="n"/>
-      <c r="S34" s="9" t="n"/>
-      <c r="T34" s="9" t="n"/>
-      <c r="U34" s="9" t="n"/>
-      <c r="V34" s="9" t="n"/>
-      <c r="W34" s="9" t="n"/>
-      <c r="X34" s="9" t="n"/>
-      <c r="Y34" s="9" t="n"/>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t>Automatique
+(TD - Salle 23)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="S34" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 24)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="T34" s="6" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="U34" s="7" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 26)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="V34" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="X34" s="11" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="Y34" s="15" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 30)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="Z34" s="9" t="n"/>
       <c r="AA34" s="9" t="n"/>
       <c r="AB34" s="9" t="n"/>
@@ -3276,14 +3222,62 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n"/>
-      <c r="S35" s="9" t="n"/>
-      <c r="T35" s="9" t="n"/>
-      <c r="U35" s="9" t="n"/>
-      <c r="V35" s="9" t="n"/>
-      <c r="W35" s="9" t="n"/>
-      <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="9" t="n"/>
+      <c r="R35" s="10" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="S35" s="14" t="inlineStr">
+        <is>
+          <t>Electrotechnique
+(TD - Salle 24)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="T35" s="14" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 25)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="U35" s="14" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 26)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="V35" s="11" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="W35" s="8" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="X35" s="5" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 29)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="Y35" s="5" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="9" t="n"/>
       <c r="AB35" s="9" t="n"/>
@@ -3471,31 +3465,43 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(CM - Amphi 1)
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Analyse 4
+(CM - Amphi 3)
 Section: MSD S4</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>Analyse 4
-(CM - Amphi 4)
+(TD - Salle 23)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
 Section: MSD S4</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
       <c r="F4" s="20" t="n"/>
-      <c r="G4" s="29" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(CM - Amphi 1)
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(CM - Amphi 2)
 Section: MSD S4</t>
         </is>
       </c>
-      <c r="H4" s="21" t="n"/>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>Inférence Statistique et Applications
+(TD - Salle 30)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n"/>
@@ -3613,19 +3619,31 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="21" t="n"/>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 25)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(CM - Amphi 3)
+Section: MSD S4</t>
+        </is>
+      </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 26)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="E16" s="21" t="n"/>
       <c r="F16" s="20" t="n"/>
       <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
+(CM - Amphi 2)
+Section: MSD S4</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n"/>
@@ -3743,37 +3761,13 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(TD - Salle 30)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>Inférence Statistique et Applications
-(CM - Amphi 3)
-Section: MSD S4</t>
-        </is>
-      </c>
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="21" t="n"/>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="21" t="n"/>
       <c r="F28" s="20" t="n"/>
-      <c r="G28" s="24" t="inlineStr">
-        <is>
-          <t>Analyse 4
-(TD - Salle 23)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 23)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="21" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n"/>
@@ -3891,19 +3885,31 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
 Section: MSD S4</t>
         </is>
       </c>
-      <c r="C40" s="21" t="n"/>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
+(TD - Salle 24)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D40" s="20" t="n"/>
       <c r="E40" s="21" t="n"/>
       <c r="F40" s="20" t="n"/>
       <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 28)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n"/>
@@ -4021,41 +4027,29 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(TD - Salle 25)
+      <c r="B52" s="21" t="n"/>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 30)
 MSD S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 2)
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 30)
+MSD S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="22" t="inlineStr">
+        <is>
+          <t>Inférence Statistique et Applications
+(CM - Amphi 4)
 Section: MSD S4</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="25" t="inlineStr">
-        <is>
-          <t>Inférence Statistique et Applications
-(TD - Salle 27)
-MSD S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(CM - Amphi 3)
-Section: MSD S4</t>
-        </is>
-      </c>
-      <c r="H52" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 23)
-MSD S4 - Groupe: 1</t>
         </is>
       </c>
     </row>
@@ -4408,40 +4402,34 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 1</t>
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(CM - Amphi 2)
+Section: MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="D4" s="20" t="n"/>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
 (TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="26" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 24)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H4" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(CM - Amphi 2)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(CM - Amphi 1)
 Section: MSD-GC-GESE S2</t>
         </is>
       </c>
@@ -4468,7 +4456,13 @@
     </row>
     <row r="7">
       <c r="A7" s="9" t="n"/>
-      <c r="B7" s="9" t="n"/>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="9" t="n"/>
@@ -4481,18 +4475,12 @@
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n"/>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="26" t="inlineStr">
         <is>
-          <t>Analyse 2
-(TD - Salle 29)
+          <t>Langue Etrangère 2
+(TD - Salle 27)
 MSD-GC-GESE S2 - Groupe: 2</t>
         </is>
       </c>
@@ -4510,20 +4498,14 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n"/>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Algèbre 2
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
@@ -4545,26 +4527,26 @@
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="9" t="n"/>
       <c r="D12" s="9" t="n"/>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="26" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 3</t>
+MSD-GC-GESE S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="H12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
@@ -4600,33 +4582,33 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
           <t>Culture digitale
 (TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
 MSD-GC-GESE S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(CM - Amphi 2)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
+      <c r="E16" s="21" t="n"/>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="28" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>Algèbre 2
-(TD - Salle 24)
+(TD - Salle 25)
 MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 1</t>
         </is>
       </c>
     </row>
@@ -4662,11 +4644,17 @@
     </row>
     <row r="20">
       <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Analyse 2
-(TD - Salle 29)
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 24)
 MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
@@ -4674,11 +4662,11 @@
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="9" t="n"/>
       <c r="G20" s="9" t="n"/>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H20" s="26" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
 (TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 1</t>
+MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4702,18 @@
     </row>
     <row r="24">
       <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 1</t>
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 3</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
@@ -4728,9 +4722,9 @@
       <c r="G24" s="9" t="n"/>
       <c r="H24" s="26" t="inlineStr">
         <is>
-          <t>Mecanique du point / Optique
+          <t>Thermodynamique &amp; Mec. du Fluide
 (TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 2</t>
+MSD-GC-GESE S2 - Groupe: 5</t>
         </is>
       </c>
     </row>
@@ -4770,40 +4764,34 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>Mecanique du point / Optique
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 3</t>
+(TD - Salle 30)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(CM - Amphi 4)
+Section: MSD-GC-GESE S2</t>
         </is>
       </c>
       <c r="D28" s="20" t="n"/>
-      <c r="E28" s="27" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="E28" s="21" t="n"/>
       <c r="F28" s="20" t="n"/>
       <c r="G28" s="22" t="inlineStr">
         <is>
           <t>Structure de la matière
-(CM - Amphi 1)
-Section: MSD-GC-GESE S2</t>
-        </is>
-      </c>
-      <c r="H28" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
+(TD - Salle 23)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 26)
 MSD-GC-GESE S2 - Groupe: 3</t>
         </is>
       </c>
@@ -4831,13 +4819,7 @@
     <row r="31">
       <c r="A31" s="9" t="n"/>
       <c r="B31" s="9" t="n"/>
-      <c r="C31" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="9" t="n"/>
@@ -4849,15 +4831,15 @@
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="9" t="n"/>
       <c r="D32" s="9" t="n"/>
-      <c r="E32" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="E32" s="9" t="n"/>
       <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="H32" s="9" t="n"/>
     </row>
     <row r="33">
@@ -4872,29 +4854,23 @@
     </row>
     <row r="34">
       <c r="A34" s="9" t="n"/>
-      <c r="B34" s="27" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="B34" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n"/>
-      <c r="H34" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 2</t>
+      <c r="H34" s="26" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 1</t>
         </is>
       </c>
     </row>
@@ -4913,27 +4889,21 @@
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="9" t="n"/>
       <c r="D36" s="9" t="n"/>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="E36" s="9" t="n"/>
       <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 30)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="H36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n"/>
       <c r="B37" s="9" t="n"/>
-      <c r="C37" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 26)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="C37" s="9" t="n"/>
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="9" t="n"/>
@@ -4966,33 +4936,39 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n"/>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 30)
+MSD-GC-GESE S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 30)
 MSD-GC-GESE S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="D40" s="20" t="n"/>
-      <c r="E40" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 5</t>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 30)
+MSD-GC-GESE S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="F40" s="20" t="n"/>
-      <c r="G40" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
+      <c r="G40" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (CM - Amphi 1)
 Section: MSD-GC-GESE S2</t>
         </is>
       </c>
-      <c r="H40" s="26" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
 (CM - Amphi 1)
 Section: MSD-GC-GESE S2</t>
         </is>
@@ -5023,23 +4999,29 @@
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="9" t="n"/>
       <c r="D43" s="9" t="n"/>
-      <c r="E43" s="27" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="E43" s="9" t="n"/>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
       <c r="H43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n"/>
-      <c r="B44" s="9" t="n"/>
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="C44" s="9" t="n"/>
       <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 28)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n"/>
       <c r="H44" s="9" t="n"/>
@@ -5057,21 +5039,9 @@
     <row r="46">
       <c r="A46" s="9" t="n"/>
       <c r="B46" s="9" t="n"/>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="C46" s="9" t="n"/>
       <c r="D46" s="9" t="n"/>
-      <c r="E46" s="26" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="E46" s="9" t="n"/>
       <c r="F46" s="9" t="n"/>
       <c r="G46" s="9" t="n"/>
       <c r="H46" s="9" t="n"/>
@@ -5088,10 +5058,22 @@
     </row>
     <row r="48">
       <c r="A48" s="9" t="n"/>
-      <c r="B48" s="9" t="n"/>
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="C48" s="9" t="n"/>
       <c r="D48" s="9" t="n"/>
-      <c r="E48" s="9" t="n"/>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 24)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="F48" s="9" t="n"/>
       <c r="G48" s="9" t="n"/>
       <c r="H48" s="9" t="n"/>
@@ -5101,13 +5083,7 @@
       <c r="B49" s="9" t="n"/>
       <c r="C49" s="9" t="n"/>
       <c r="D49" s="9" t="n"/>
-      <c r="E49" s="26" t="inlineStr">
-        <is>
-          <t>Mecanique du point / Optique
-(TD - Salle 27)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="E49" s="9" t="n"/>
       <c r="F49" s="9" t="n"/>
       <c r="G49" s="9" t="n"/>
       <c r="H49" s="9" t="n"/>
@@ -5138,35 +5114,41 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 30)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="C52" s="27" t="inlineStr">
         <is>
           <t>Culture digitale
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="26" t="inlineStr">
-        <is>
-          <t>Analyse 2
 (CM - Amphi 2)
 Section: MSD-GC-GESE S2</t>
         </is>
       </c>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(CM - Amphi 1)
+Section: MSD-GC-GESE S2</t>
+        </is>
+      </c>
       <c r="F52" s="20" t="n"/>
-      <c r="G52" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 23)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H52" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
+      <c r="G52" s="26" t="inlineStr">
+        <is>
+          <t>Thermodynamique &amp; Mec. du Fluide
+(TD - Salle 24)
 MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
     </row>
@@ -5202,31 +5184,25 @@
     </row>
     <row r="56">
       <c r="A56" s="9" t="n"/>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="28" t="inlineStr">
+      <c r="B56" s="25" t="inlineStr">
         <is>
           <t>Algèbre 2
 (TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 1</t>
-        </is>
-      </c>
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n"/>
       <c r="D56" s="9" t="n"/>
       <c r="E56" s="9" t="n"/>
       <c r="F56" s="9" t="n"/>
-      <c r="G56" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 25)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="H56" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 29)
-MSD-GC-GESE S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="G56" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n"/>
@@ -5260,31 +5236,25 @@
     </row>
     <row r="60">
       <c r="A60" s="9" t="n"/>
-      <c r="B60" s="9" t="n"/>
-      <c r="C60" s="27" t="inlineStr">
-        <is>
-          <t>Thermodynamique &amp; Mec. du Fluide
-(TD - Salle 30)
-MSD-GC-GESE S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 26)
+MSD-GC-GESE S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n"/>
       <c r="D60" s="9" t="n"/>
       <c r="E60" s="9" t="n"/>
       <c r="F60" s="9" t="n"/>
-      <c r="G60" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 27)
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 28)
 MSD-GC-GESE S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="H60" s="26" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 28)
-MSD-GC-GESE S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="H60" s="9" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n"/>
@@ -5322,8 +5292,20 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 25)
+MSD-GC-GESE S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="C64" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
       <c r="D64" s="20" t="n"/>
       <c r="E64" s="21" t="n"/>
       <c r="F64" s="20" t="n"/>
@@ -5362,7 +5344,13 @@
     </row>
     <row r="68">
       <c r="A68" s="9" t="n"/>
-      <c r="B68" s="9" t="n"/>
+      <c r="B68" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 27)
+MSD-GC-GESE S2 - Groupe: 6</t>
+        </is>
+      </c>
       <c r="C68" s="9" t="n"/>
       <c r="D68" s="9" t="n"/>
       <c r="E68" s="9" t="n"/>
@@ -5402,7 +5390,13 @@
     </row>
     <row r="72">
       <c r="A72" s="9" t="n"/>
-      <c r="B72" s="9" t="n"/>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>Mecanique du point / Optique
+(TD - Salle 30)
+MSD-GC-GESE S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="C72" s="9" t="n"/>
       <c r="D72" s="9" t="n"/>
       <c r="E72" s="9" t="n"/>
@@ -5441,83 +5435,81 @@
       <c r="H75" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="76">
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="B40:B51"/>
+  <mergeCells count="74">
+    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="A4:A15"/>
     <mergeCell ref="G52:G55"/>
-    <mergeCell ref="A4:A15"/>
-    <mergeCell ref="E8:E11"/>
     <mergeCell ref="F52:F63"/>
     <mergeCell ref="F28:F39"/>
     <mergeCell ref="G8:G11"/>
-    <mergeCell ref="B64:B75"/>
     <mergeCell ref="C20:C23"/>
+    <mergeCell ref="B72:B75"/>
     <mergeCell ref="D64:D75"/>
+    <mergeCell ref="G36:G39"/>
     <mergeCell ref="F64:F75"/>
     <mergeCell ref="A28:A39"/>
     <mergeCell ref="G16:G27"/>
-    <mergeCell ref="B16:B27"/>
+    <mergeCell ref="C28:C39"/>
+    <mergeCell ref="E48:E51"/>
     <mergeCell ref="G40:G51"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="G28:G31"/>
+    <mergeCell ref="A40:A51"/>
     <mergeCell ref="E16:E27"/>
-    <mergeCell ref="A40:A51"/>
+    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="B4:B6"/>
     <mergeCell ref="H34:H39"/>
     <mergeCell ref="A52:A63"/>
-    <mergeCell ref="H56:H59"/>
     <mergeCell ref="E52:E63"/>
     <mergeCell ref="H4:H15"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="A64:A75"/>
     <mergeCell ref="C16:C19"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="E28:E31"/>
-    <mergeCell ref="C56:C59"/>
-    <mergeCell ref="C10:C15"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="A64:A75"/>
     <mergeCell ref="C64:C75"/>
     <mergeCell ref="E64:E75"/>
+    <mergeCell ref="B7:B9"/>
     <mergeCell ref="F4:F15"/>
-    <mergeCell ref="H52:H55"/>
+    <mergeCell ref="B48:B51"/>
     <mergeCell ref="D40:D51"/>
-    <mergeCell ref="C46:C51"/>
+    <mergeCell ref="E40:E43"/>
     <mergeCell ref="F40:F51"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E36:E39"/>
-    <mergeCell ref="C52:C55"/>
-    <mergeCell ref="H60:H63"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="C4:C15"/>
     <mergeCell ref="F16:F27"/>
-    <mergeCell ref="B52:B63"/>
+    <mergeCell ref="E4:E15"/>
     <mergeCell ref="D52:D63"/>
-    <mergeCell ref="C60:C63"/>
     <mergeCell ref="G4:G7"/>
     <mergeCell ref="H16:H19"/>
     <mergeCell ref="B34:B39"/>
+    <mergeCell ref="B68:B71"/>
     <mergeCell ref="H64:H75"/>
-    <mergeCell ref="B10:B15"/>
     <mergeCell ref="B28:B33"/>
-    <mergeCell ref="C40:C45"/>
-    <mergeCell ref="G28:G39"/>
+    <mergeCell ref="E28:E39"/>
+    <mergeCell ref="B24:B27"/>
     <mergeCell ref="H40:H51"/>
     <mergeCell ref="H28:H33"/>
-    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="H52:H63"/>
     <mergeCell ref="A16:A27"/>
-    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="C40:C51"/>
     <mergeCell ref="G60:G63"/>
-    <mergeCell ref="E49:E51"/>
+    <mergeCell ref="B10:B12"/>
     <mergeCell ref="D4:D15"/>
+    <mergeCell ref="C52:C63"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B20:B23"/>
     <mergeCell ref="G56:G59"/>
-    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="B64:B67"/>
     <mergeCell ref="D16:D27"/>
     <mergeCell ref="G64:G75"/>
     <mergeCell ref="G12:G15"/>
     <mergeCell ref="H24:H27"/>
     <mergeCell ref="H20:H23"/>
     <mergeCell ref="D28:D39"/>
-    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="B16:B19"/>
     <mergeCell ref="C24:C27"/>
-    <mergeCell ref="E40:E42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5585,28 +5577,34 @@
       <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Développement Personnel
-(TD - Salle 26)
+(TD - Salle 30)
 GB S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>Biologie Moléculaire et Génétique
-(TD - Salle 26)
-GB S4 - Groupe: 1</t>
+          <t>Biochimie Métabolique et Enzymologie
+(CM - Amphi 3)
+Section: GB S4</t>
         </is>
       </c>
       <c r="D4" s="20" t="n"/>
       <c r="E4" s="21" t="n"/>
       <c r="F4" s="20" t="n"/>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 2)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="n"/>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>Physiologie Animale et Végétale
+(TD - Salle 30)
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique
+(TD - Salle 23)
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n"/>
@@ -5724,30 +5722,24 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 2)
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Physiologie Animale et Végétale
+(CM - Amphi 3)
 Section: GB S4</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
-(CM - Amphi 2)
-Section: GB S4</t>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 28)
+GB S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="D16" s="20" t="n"/>
       <c r="E16" s="21" t="n"/>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>Biologie Moléculaire et Génétique
-(CM - Amphi 3)
-Section: GB S4</t>
-        </is>
-      </c>
+      <c r="G16" s="21" t="n"/>
       <c r="H16" s="21" t="n"/>
     </row>
     <row r="17">
@@ -5867,30 +5859,18 @@
         </is>
       </c>
       <c r="B28" s="21" t="n"/>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(CM - Amphi 1)
-Section: GB S4</t>
-        </is>
-      </c>
+      <c r="C28" s="21" t="n"/>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="21" t="n"/>
       <c r="F28" s="20" t="n"/>
-      <c r="G28" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 29)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t>Physiologie Animale et Végétale
-(TD - Salle 26)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(CM - Amphi 1)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n"/>
@@ -6008,31 +5988,31 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>Physiologie Animale et Végétale
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>Biochimie Métabolique et Enzymologie
+(TD - Salle 23)
+GB S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>Analyse de Données
 (CM - Amphi 3)
 Section: GB S4</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(TD - Salle 30)
-GB S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(CM - Amphi 1)
-Section: GB S4</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n"/>
@@ -6150,31 +6130,37 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="23" t="inlineStr">
-        <is>
-          <t>Biochimie Métabolique et Enzymologie
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>Biologie Moléculaire et Génétique
 (CM - Amphi 3)
 Section: GB S4</t>
         </is>
       </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="23" t="inlineStr">
-        <is>
-          <t>Biochimie Métabolique et Enzymologie
+      <c r="C52" s="25" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
 (TD - Salle 26)
 GB S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="H52" s="19" t="inlineStr">
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="25" t="inlineStr">
         <is>
           <t>Méthodes d'analyse
-(TD - Salle 27)
+(CM - Amphi 2)
+Section: GB S4</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 29)
 GB S4 - Groupe: 1</t>
         </is>
       </c>
+      <c r="H52" s="21" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n"/>
@@ -6525,35 +6511,35 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 27)
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(CM - Amphi 2)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 29)
 GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="D4" s="20" t="n"/>
       <c r="E4" s="21" t="n"/>
       <c r="F4" s="20" t="n"/>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t>Réactivité Chimique
-(TD - Salle 30)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="H4" s="19" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 4</t>
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 6</t>
         </is>
       </c>
     </row>
@@ -6585,23 +6571,11 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="H7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n"/>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="B8" s="9" t="n"/>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
@@ -6622,16 +6596,28 @@
     <row r="10">
       <c r="A10" s="9" t="n"/>
       <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t>Réactivité Chimique
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
 (TD - Salle 25)
-GB-GEG S2 - Groupe: 6</t>
+GB-GEG S2 - Groupe: 3</t>
         </is>
       </c>
     </row>
@@ -6647,13 +6633,7 @@
     </row>
     <row r="12">
       <c r="A12" s="9" t="n"/>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="n"/>
       <c r="C12" s="9" t="n"/>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
@@ -6669,13 +6649,7 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="25" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 27)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="H13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n"/>
@@ -6706,37 +6680,31 @@
       <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Biologie Animale et Végétale
-(TD - Salle 28)
+(TD - Salle 29)
 GB-GEG S2 - Groupe: 5</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(CM - Amphi 1)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Langue Etrangère 2
 (TD - Salle 25)
-GB-GEG S2 - Groupe: 3</t>
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>Biologie Animale et Végétale
-(CM - Amphi 2)
+          <t>Bases de Données
+(CM - Amphi 4)
 Section: GB-GEG S2</t>
         </is>
       </c>
@@ -6758,17 +6726,23 @@
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="9" t="n"/>
-      <c r="G18" s="9" t="n"/>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 23)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
       <c r="H18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n"/>
       <c r="B19" s="9" t="n"/>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
 (TD - Salle 27)
-GB-GEG S2 - Groupe: 5</t>
+GB-GEG S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
@@ -6779,18 +6753,18 @@
     </row>
     <row r="20">
       <c r="A20" s="9" t="n"/>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="B20" s="9" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="H20" s="9" t="n"/>
     </row>
     <row r="21">
@@ -6805,18 +6779,30 @@
     </row>
     <row r="22">
       <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 2</t>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 1</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="H22" s="9" t="n"/>
     </row>
     <row r="23">
@@ -6831,28 +6817,28 @@
     </row>
     <row r="24">
       <c r="A24" s="9" t="n"/>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="B24" s="9" t="n"/>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="H24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n"/>
       <c r="B25" s="9" t="n"/>
-      <c r="C25" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 1</t>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 3</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
@@ -6887,39 +6873,39 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(CM - Amphi 4)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
 (TD - Salle 24)
 GB-GEG S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(CM - Amphi 4)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="24" t="inlineStr">
+      <c r="H28" s="19" t="inlineStr">
         <is>
           <t>Mécanique des Fluides et Transfert Thermique
-(CM - Amphi 4)
-Section: GB-GEG S2</t>
-        </is>
-      </c>
-      <c r="H28" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
 (CM - Amphi 1)
 Section: GB-GEG S2</t>
         </is>
@@ -6947,13 +6933,7 @@
     </row>
     <row r="31">
       <c r="A31" s="9" t="n"/>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="B31" s="9" t="n"/>
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
@@ -6963,12 +6943,18 @@
     </row>
     <row r="32">
       <c r="A32" s="9" t="n"/>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 3</t>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 6</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
@@ -6989,18 +6975,18 @@
     </row>
     <row r="34">
       <c r="A34" s="9" t="n"/>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="B34" s="9" t="n"/>
       <c r="C34" s="9" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
+      <c r="G34" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="H34" s="9" t="n"/>
     </row>
     <row r="35">
@@ -7015,12 +7001,18 @@
     </row>
     <row r="36">
       <c r="A36" s="9" t="n"/>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="25" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 27)
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 29)
 GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 24)
+GB-GEG S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
@@ -7031,13 +7023,7 @@
     </row>
     <row r="37">
       <c r="A37" s="9" t="n"/>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="B37" s="9" t="n"/>
       <c r="C37" s="9" t="n"/>
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="9" t="n"/>
@@ -7071,37 +7057,37 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="B40" s="27" t="inlineStr">
         <is>
           <t>Culture digitale
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="H40" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
 (CM - Amphi 2)
 Section: GB-GEG S2</t>
         </is>
       </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(CM - Amphi 1)
+Section: GB-GEG S2</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="H40" s="21" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n"/>
@@ -7130,24 +7116,18 @@
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="9" t="n"/>
       <c r="F43" s="9" t="n"/>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
+      <c r="G43" s="25" t="inlineStr">
+        <is>
+          <t>Bases de Données
 (TD - Salle 24)
-GB-GEG S2 - Groupe: 6</t>
+GB-GEG S2 - Groupe: 5</t>
         </is>
       </c>
       <c r="H43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="9" t="n"/>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(TD - Salle 30)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="B44" s="9" t="n"/>
       <c r="C44" s="9" t="n"/>
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
@@ -7168,21 +7148,21 @@
     <row r="46">
       <c r="A46" s="9" t="n"/>
       <c r="B46" s="9" t="n"/>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 24)
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 23)
 GB-GEG S2 - Groupe: 3</t>
         </is>
       </c>
       <c r="D46" s="9" t="n"/>
       <c r="E46" s="9" t="n"/>
       <c r="F46" s="9" t="n"/>
-      <c r="G46" s="25" t="inlineStr">
-        <is>
-          <t>Biologie Animale et Végétale
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 4</t>
+      <c r="G46" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
       <c r="H46" s="9" t="n"/>
@@ -7199,13 +7179,7 @@
     </row>
     <row r="48">
       <c r="A48" s="9" t="n"/>
-      <c r="B48" s="25" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="B48" s="9" t="n"/>
       <c r="C48" s="9" t="n"/>
       <c r="D48" s="9" t="n"/>
       <c r="E48" s="9" t="n"/>
@@ -7220,11 +7194,11 @@
       <c r="D49" s="9" t="n"/>
       <c r="E49" s="9" t="n"/>
       <c r="F49" s="9" t="n"/>
-      <c r="G49" s="19" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 27)
-GB-GEG S2 - Groupe: 1</t>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 4</t>
         </is>
       </c>
       <c r="H49" s="9" t="n"/>
@@ -7255,41 +7229,35 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="25" t="inlineStr">
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>Géodynamique externe
+(TD - Salle 23)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="inlineStr">
         <is>
           <t>Biologie Animale et Végétale
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 26)
-GB-GEG S2 - Groupe: 1</t>
+(CM - Amphi 1)
+Section: GB-GEG S2</t>
         </is>
       </c>
       <c r="D52" s="20" t="n"/>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>Mécanique des Fluides et Transfert Thermique
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="25" t="inlineStr">
+        <is>
+          <t>Bases de Données
 (TD - Salle 30)
 GB-GEG S2 - Groupe: 2</t>
         </is>
       </c>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="25" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 29)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="H52" s="18" t="inlineStr">
-        <is>
-          <t>Réactivité Chimique
-(CM - Amphi 4)
-Section: GB-GEG S2</t>
+      <c r="H52" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 1</t>
         </is>
       </c>
     </row>
@@ -7318,13 +7286,7 @@
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="9" t="n"/>
       <c r="D55" s="9" t="n"/>
-      <c r="E55" s="19" t="inlineStr">
-        <is>
-          <t>Bases de Données
-(TD - Salle 28)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="E55" s="9" t="n"/>
       <c r="F55" s="9" t="n"/>
       <c r="G55" s="9" t="n"/>
       <c r="H55" s="9" t="n"/>
@@ -7336,8 +7298,20 @@
       <c r="D56" s="9" t="n"/>
       <c r="E56" s="9" t="n"/>
       <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="9" t="n"/>
+      <c r="G56" s="19" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 23)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="H56" s="19" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 6</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n"/>
@@ -7352,29 +7326,11 @@
     <row r="58">
       <c r="A58" s="9" t="n"/>
       <c r="B58" s="9" t="n"/>
-      <c r="C58" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="C58" s="9" t="n"/>
       <c r="D58" s="9" t="n"/>
-      <c r="E58" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 25)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="E58" s="9" t="n"/>
       <c r="F58" s="9" t="n"/>
-      <c r="G58" s="25" t="inlineStr">
-        <is>
-          <t>Géodynamique externe
-(TD - Salle 24)
-GB-GEG S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="G58" s="9" t="n"/>
       <c r="H58" s="9" t="n"/>
     </row>
     <row r="59">
@@ -7394,21 +7350,27 @@
       <c r="D60" s="9" t="n"/>
       <c r="E60" s="9" t="n"/>
       <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
-      <c r="H60" s="9" t="n"/>
+      <c r="G60" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 25)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="H60" s="25" t="inlineStr">
+        <is>
+          <t>Biologie Animale et Végétale
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 4</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="9" t="n"/>
       <c r="D61" s="9" t="n"/>
-      <c r="E61" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 23)
-GB-GEG S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="E61" s="9" t="n"/>
       <c r="F61" s="9" t="n"/>
       <c r="G61" s="9" t="n"/>
       <c r="H61" s="9" t="n"/>
@@ -7439,8 +7401,20 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="26" t="inlineStr">
+        <is>
+          <t>Réactivité Chimique
+(TD - Salle 29)
+GB-GEG S2 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 27)
+GB-GEG S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="D64" s="20" t="n"/>
       <c r="E64" s="21" t="n"/>
       <c r="F64" s="20" t="n"/>
@@ -7480,7 +7454,13 @@
     <row r="68">
       <c r="A68" s="9" t="n"/>
       <c r="B68" s="9" t="n"/>
-      <c r="C68" s="9" t="n"/>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>Mécanique des Fluides et Transfert Thermique
+(TD - Salle 28)
+GB-GEG S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="D68" s="9" t="n"/>
       <c r="E68" s="9" t="n"/>
       <c r="F68" s="9" t="n"/>
@@ -7520,7 +7500,13 @@
     <row r="72">
       <c r="A72" s="9" t="n"/>
       <c r="B72" s="9" t="n"/>
-      <c r="C72" s="9" t="n"/>
+      <c r="C72" s="25" t="inlineStr">
+        <is>
+          <t>Bases de Données
+(TD - Salle 30)
+GB-GEG S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D72" s="9" t="n"/>
       <c r="E72" s="9" t="n"/>
       <c r="F72" s="9" t="n"/>
@@ -7559,81 +7545,81 @@
     </row>
   </sheetData>
   <mergeCells count="75">
+    <mergeCell ref="B40:B51"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="G52:G55"/>
     <mergeCell ref="A4:A15"/>
-    <mergeCell ref="G4:G15"/>
-    <mergeCell ref="H7:H9"/>
     <mergeCell ref="H16:H27"/>
-    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="H4:H9"/>
+    <mergeCell ref="F52:F63"/>
     <mergeCell ref="F28:F39"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="F52:F63"/>
+    <mergeCell ref="B64:B75"/>
     <mergeCell ref="H28:H39"/>
-    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="C64:C67"/>
     <mergeCell ref="D64:D75"/>
     <mergeCell ref="F64:F75"/>
-    <mergeCell ref="C58:C63"/>
-    <mergeCell ref="C22:C24"/>
     <mergeCell ref="A28:A39"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="G16:G27"/>
-    <mergeCell ref="G52:G57"/>
+    <mergeCell ref="H10:H15"/>
     <mergeCell ref="G40:G42"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="E16:E27"/>
     <mergeCell ref="A40:A51"/>
-    <mergeCell ref="E16:E27"/>
     <mergeCell ref="A52:A63"/>
-    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="H56:H59"/>
+    <mergeCell ref="E52:E63"/>
     <mergeCell ref="A64:A75"/>
     <mergeCell ref="G43:G45"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="C64:C75"/>
+    <mergeCell ref="C10:C15"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="E64:E75"/>
+    <mergeCell ref="G34:G39"/>
+    <mergeCell ref="G10:G15"/>
     <mergeCell ref="F4:F15"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G28:G33"/>
+    <mergeCell ref="G24:G27"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="C46:C51"/>
     <mergeCell ref="G46:G48"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="D40:D51"/>
-    <mergeCell ref="E58:E60"/>
-    <mergeCell ref="C46:C51"/>
     <mergeCell ref="F40:F51"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="C4:C15"/>
+    <mergeCell ref="H52:H55"/>
+    <mergeCell ref="H60:H63"/>
     <mergeCell ref="F16:F27"/>
     <mergeCell ref="E4:E15"/>
     <mergeCell ref="B52:B63"/>
     <mergeCell ref="D52:D63"/>
-    <mergeCell ref="H10:H12"/>
     <mergeCell ref="C36:C39"/>
     <mergeCell ref="H64:H75"/>
     <mergeCell ref="C40:C45"/>
-    <mergeCell ref="G58:G63"/>
+    <mergeCell ref="C72:C75"/>
     <mergeCell ref="E28:E39"/>
-    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="G16:G17"/>
     <mergeCell ref="C32:C35"/>
-    <mergeCell ref="G28:G39"/>
     <mergeCell ref="H40:H51"/>
-    <mergeCell ref="C52:C57"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B36:B39"/>
     <mergeCell ref="C28:C31"/>
-    <mergeCell ref="H52:H63"/>
     <mergeCell ref="A16:A27"/>
+    <mergeCell ref="G60:G63"/>
+    <mergeCell ref="G4:G9"/>
     <mergeCell ref="E40:E51"/>
     <mergeCell ref="C25:C27"/>
     <mergeCell ref="D4:D15"/>
-    <mergeCell ref="B4:B7"/>
     <mergeCell ref="C16:C18"/>
-    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C52:C63"/>
+    <mergeCell ref="G56:G59"/>
     <mergeCell ref="D16:D27"/>
     <mergeCell ref="G64:G75"/>
-    <mergeCell ref="E61:E63"/>
+    <mergeCell ref="C68:C71"/>
     <mergeCell ref="D28:D39"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="B32:B35"/>
     <mergeCell ref="G49:G51"/>
-    <mergeCell ref="B37:B39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7698,25 +7684,37 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>Chimie Organique 2
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Éléments de Génie Chimique
+(TD - Salle 27)
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (CM - Amphi 2)
 Section: GC S4</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>Thermodynamique Chimique et Cinétique
-(CM - Amphi 1)
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>Chimie Minérale 2
+(CM - Amphi 4)
 Section: GC S4</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="21" t="n"/>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 28)
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n"/>
@@ -7834,16 +7832,16 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Chimie Organique 2
-(TD - Salle 29)
+(TD - Salle 23)
 GC S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Éléments de Génie Chimique
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Thermodynamique Chimique et Cinétique
 (CM - Amphi 4)
 Section: GC S4</t>
         </is>
@@ -7853,15 +7851,15 @@
       <c r="F16" s="20" t="n"/>
       <c r="G16" s="18" t="inlineStr">
         <is>
-          <t>Analyse de Données
-(CM - Amphi 1)
-Section: GC S4</t>
-        </is>
-      </c>
-      <c r="H16" s="27" t="inlineStr">
-        <is>
-          <t>Chimie Minérale 2
-(TD - Salle 28)
+          <t>Développement Personnel
+(TD - Salle 26)
+GC S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 30)
 GC S4 - Groupe: 1</t>
         </is>
       </c>
@@ -7982,23 +7980,29 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 30)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>Chimie Organique 2
+(CM - Amphi 4)
+Section: GC S4</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="n"/>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="21" t="n"/>
       <c r="F28" s="20" t="n"/>
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 29)
-GC S4 - Groupe: 1</t>
+      <c r="G28" s="28" t="inlineStr">
+        <is>
+          <t>Éléments de Génie Chimique
+(CM - Amphi 2)
+Section: GC S4</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(CM - Amphi 3)
+Section: GC S4</t>
         </is>
       </c>
     </row>
@@ -8118,9 +8122,9 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
 Section: GC S4</t>
         </is>
@@ -8129,9 +8133,9 @@
       <c r="D40" s="20" t="n"/>
       <c r="E40" s="21" t="n"/>
       <c r="F40" s="20" t="n"/>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>Analyse de Données
+      <c r="G40" s="27" t="inlineStr">
+        <is>
+          <t>Chimie Minérale 2
 (TD - Salle 30)
 GC S4 - Groupe: 1</t>
         </is>
@@ -8139,7 +8143,7 @@
       <c r="H40" s="26" t="inlineStr">
         <is>
           <t>Thermodynamique Chimique et Cinétique
-(TD - Salle 26)
+(TD - Salle 30)
 GC S4 - Groupe: 1</t>
         </is>
       </c>
@@ -8260,28 +8264,10 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr">
-        <is>
-          <t>Chimie Minérale 2
-(CM - Amphi 1)
-Section: GC S4</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 2)
-Section: GC S4</t>
-        </is>
-      </c>
+      <c r="B52" s="21" t="n"/>
+      <c r="C52" s="21" t="n"/>
       <c r="D52" s="20" t="n"/>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>Éléments de Génie Chimique
-(TD - Salle 29)
-GC S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="E52" s="21" t="n"/>
       <c r="F52" s="20" t="n"/>
       <c r="G52" s="21" t="n"/>
       <c r="H52" s="21" t="n"/>
@@ -8635,31 +8621,31 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Analyse de Données
+(TD - Salle 28)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Géologie Structurale
-(CM - Amphi 2)
+(CM - Amphi 1)
 Section: GEG S4</t>
         </is>
       </c>
       <c r="D4" s="20" t="n"/>
       <c r="E4" s="21" t="n"/>
       <c r="F4" s="20" t="n"/>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 2)
-Section: GEG S4</t>
-        </is>
-      </c>
-      <c r="H4" s="27" t="inlineStr">
-        <is>
-          <t>Pétrographie et Minéralogie
-(TD - Salle 30)
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
+(TD - Salle 26)
 GEG S4 - Groupe: 1</t>
         </is>
       </c>
+      <c r="H4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n"/>
@@ -8777,30 +8763,12 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>Géomatique
-(TD - Salle 26)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
-(CM - Amphi 2)
-Section: GEG S4</t>
-        </is>
-      </c>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
       <c r="D16" s="20" t="n"/>
       <c r="E16" s="21" t="n"/>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 29)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="G16" s="21" t="n"/>
       <c r="H16" s="21" t="n"/>
     </row>
     <row r="17">
@@ -8919,19 +8887,37 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 26)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>LTC2 Français
-(CM - Amphi 1)
-Section: GEG S4</t>
+(TD - Salle 23)
+GEG S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="21" t="n"/>
       <c r="F28" s="20" t="n"/>
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="21" t="n"/>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(CM - Amphi 1)
+Section: GEG S4</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>Pétrographie et Minéralogie
+(TD - Salle 28)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n"/>
@@ -9049,41 +9035,23 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
+Section: GEG S4</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="24" t="inlineStr">
         <is>
           <t>Analyse de Données
-(TD - Salle 25)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C40" s="27" t="inlineStr">
-        <is>
-          <t>Géologie Structurale
-(TD - Salle 29)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>Analyse de Données
-(CM - Amphi 1)
+(CM - Amphi 3)
 Section: GEG S4</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 26)
-GEG S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>Méthodes d'analyse
-(TD - Salle 27)
-GEG S4 - Groupe: 1</t>
         </is>
       </c>
     </row>
@@ -9203,25 +9171,43 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr">
+      <c r="B52" s="22" t="inlineStr">
         <is>
           <t>Pétrographie et Minéralogie
+(CM - Amphi 4)
+Section: GEG S4</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Géologie Structurale
+(TD - Salle 23)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="25" t="inlineStr">
+        <is>
+          <t>Méthodes d'analyse
 (CM - Amphi 2)
 Section: GEG S4</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="28" t="inlineStr">
         <is>
           <t>Géomatique
 (CM - Amphi 4)
 Section: GEG S4</t>
         </is>
       </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="21" t="n"/>
+      <c r="H52" s="28" t="inlineStr">
+        <is>
+          <t>Géomatique
+(TD - Salle 23)
+GEG S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n"/>
@@ -9572,25 +9558,37 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
-        <is>
-          <t>Métrologie Capteurs
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Automatique
 (CM - Amphi 4)
 Section: GESE S4</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
+Section: GESE S4</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>Electrotechnique
 (CM - Amphi 3)
 Section: GESE S4</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="21" t="n"/>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(TD - Salle 26)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n"/>
@@ -9708,34 +9706,34 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>Electrotechnique
-(TD - Salle 27)
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 30)
 GESE S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>Automatique
-(CM - Amphi 3)
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(CM - Amphi 2)
 Section: GESE S4</t>
         </is>
       </c>
       <c r="D16" s="20" t="n"/>
       <c r="E16" s="21" t="n"/>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(CM - Amphi 2)
-Section: GESE S4</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 28)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>LTC2 Français
-(TD - Salle 26)
+(TD - Salle 23)
 GESE S4 - Groupe: 1</t>
         </is>
       </c>
@@ -9856,12 +9854,24 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Métrologie Capteurs
+(CM - Amphi 2)
+Section: GESE S4</t>
+        </is>
+      </c>
       <c r="C28" s="21" t="n"/>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="21" t="n"/>
       <c r="F28" s="20" t="n"/>
-      <c r="G28" s="21" t="n"/>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(CM - Amphi 3)
+Section: GESE S4</t>
+        </is>
+      </c>
       <c r="H28" s="21" t="n"/>
     </row>
     <row r="29">
@@ -9980,37 +9990,19 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
 Section: GESE S4</t>
         </is>
       </c>
-      <c r="C40" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 27)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="C40" s="21" t="n"/>
       <c r="D40" s="20" t="n"/>
       <c r="E40" s="21" t="n"/>
       <c r="F40" s="20" t="n"/>
-      <c r="G40" s="28" t="inlineStr">
-        <is>
-          <t>Métrologie Capteurs
-(TD - Salle 29)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 25)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="21" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="9" t="n"/>
@@ -10128,37 +10120,19 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 30)
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>Métrologie Capteurs
+(TD - Salle 24)
 GESE S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 2)
-Section: GESE S4</t>
-        </is>
-      </c>
+      <c r="C52" s="21" t="n"/>
       <c r="D52" s="20" t="n"/>
       <c r="E52" s="21" t="n"/>
       <c r="F52" s="20" t="n"/>
-      <c r="G52" s="25" t="inlineStr">
-        <is>
-          <t>Electrotechnique
-(CM - Amphi 1)
-Section: GESE S4</t>
-        </is>
-      </c>
-      <c r="H52" s="26" t="inlineStr">
-        <is>
-          <t>Automatique
-(TD - Salle 30)
-GESE S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="21" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n"/>
@@ -10276,8 +10250,20 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>Automatique
+(TD - Salle 23)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C64" s="29" t="inlineStr">
+        <is>
+          <t>Electrotechnique
+(TD - Salle 24)
+GESE S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D64" s="20" t="n"/>
       <c r="E64" s="21" t="n"/>
       <c r="F64" s="20" t="n"/>
@@ -10511,27 +10497,39 @@
       </c>
       <c r="B4" s="29" t="inlineStr">
         <is>
-          <t>Analyse Numérique
-(CM - Amphi 3)
+          <t>Recherche Opérationnelle
+(TD - Salle 29)
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 30)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
 Section: GI S4</t>
         </is>
       </c>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
       <c r="F4" s="20" t="n"/>
-      <c r="G4" s="29" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 23)
 GI S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 23)
-GI S4 - Groupe: 1</t>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
+(TD - Salle 24)
+GI S4 - Groupe: 3</t>
         </is>
       </c>
     </row>
@@ -10572,13 +10570,7 @@
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
-      <c r="G8" s="29" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(CM - Amphi 1)
-Section: GI S4</t>
-        </is>
-      </c>
+      <c r="G8" s="9" t="n"/>
       <c r="H8" s="9" t="n"/>
     </row>
     <row r="9">
@@ -10599,11 +10591,11 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
       <c r="G10" s="9" t="n"/>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+      <c r="H10" s="29" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
 (TD - Salle 29)
-GI S4 - Groupe: 3</t>
+GI S4 - Groupe: 2</t>
         </is>
       </c>
     </row>
@@ -10624,13 +10616,7 @@
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 27)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="G12" s="9" t="n"/>
       <c r="H12" s="9" t="n"/>
     </row>
     <row r="13">
@@ -10669,31 +10655,25 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="28" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
-(TD - Salle 30)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(TD - Salle 30)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Structure des Données
 (TD - Salle 27)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="n"/>
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
+(CM - Amphi 2)
+Section: GI S4</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n"/>
@@ -10730,7 +10710,13 @@
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 25)
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="F20" s="9" t="n"/>
       <c r="G20" s="9" t="n"/>
       <c r="H20" s="9" t="n"/>
@@ -10747,24 +10733,12 @@
     </row>
     <row r="22">
       <c r="A22" s="9" t="n"/>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 23)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="B22" s="9" t="n"/>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
-      <c r="G22" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 26)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="G22" s="9" t="n"/>
       <c r="H22" s="9" t="n"/>
     </row>
     <row r="23">
@@ -10782,7 +10756,13 @@
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>Programmation Web
+(TD - Salle 29)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="F24" s="9" t="n"/>
       <c r="G24" s="9" t="n"/>
       <c r="H24" s="9" t="n"/>
@@ -10823,29 +10803,35 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>Recherche Opérationnelle
-(CM - Amphi 4)
+(CM - Amphi 1)
 Section: GI S4</t>
         </is>
       </c>
-      <c r="C28" s="21" t="n"/>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>Programmation Web
+(TD - Salle 29)
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D28" s="20" t="n"/>
       <c r="E28" s="21" t="n"/>
       <c r="F28" s="20" t="n"/>
-      <c r="G28" s="28" t="inlineStr">
-        <is>
-          <t>Programmation Web
-(TD - Salle 28)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="H28" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>Structure des Données
 (TD - Salle 27)
 GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 30)
+GI S4 - Groupe: 3</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10868,13 @@
     <row r="32">
       <c r="A32" s="9" t="n"/>
       <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 30)
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="9" t="n"/>
@@ -10906,13 +10898,7 @@
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="9" t="n"/>
-      <c r="G34" s="19" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 27)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="G34" s="9" t="n"/>
       <c r="H34" s="9" t="n"/>
     </row>
     <row r="35">
@@ -10928,7 +10914,13 @@
     <row r="36">
       <c r="A36" s="9" t="n"/>
       <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
+      <c r="C36" s="28" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 28)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="9" t="n"/>
@@ -10971,40 +10963,34 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
 Section: GI S4</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(CM - Amphi 2)
-Section: GI S4</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="28" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
-(TD - Salle 30)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="28" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>Programmation Web
 (CM - Amphi 3)
 Section: GI S4</t>
         </is>
       </c>
-      <c r="H40" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 29)
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(CM - Amphi 3)
+Section: GI S4</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
+(TD - Salle 24)
 GI S4 - Groupe: 2</t>
         </is>
       </c>
@@ -11064,16 +11050,16 @@
       <c r="B46" s="9" t="n"/>
       <c r="C46" s="9" t="n"/>
       <c r="D46" s="9" t="n"/>
-      <c r="E46" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 28)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="E46" s="9" t="n"/>
       <c r="F46" s="9" t="n"/>
       <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
+      <c r="H46" s="29" t="inlineStr">
+        <is>
+          <t>Recherche Opérationnelle
+(TD - Salle 29)
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="n"/>
@@ -11133,39 +11119,39 @@
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
+          <t>Analyse Numérique
+(CM - Amphi 2)
+Section: GI S4</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
           <t>Programmation Web
+(TD - Salle 29)
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(TD - Salle 27)
+GI S4 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 26)
+GI S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>Systèmes d'Information et Bases de Données
 (TD - Salle 24)
 GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(CM - Amphi 2)
-Section: GI S4</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 26)
-GI S4 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="28" t="inlineStr">
-        <is>
-          <t>Programmation Web
-(TD - Salle 28)
-GI S4 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="inlineStr">
-        <is>
-          <t>Systèmes d'Information et Bases de Données
-(TD - Salle 24)
-GI S4 - Groupe: 2</t>
         </is>
       </c>
     </row>
@@ -11224,20 +11210,20 @@
       <c r="B58" s="9" t="n"/>
       <c r="C58" s="9" t="n"/>
       <c r="D58" s="9" t="n"/>
-      <c r="E58" s="9" t="n"/>
+      <c r="E58" s="28" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 28)
+GI S4 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="F58" s="9" t="n"/>
-      <c r="G58" s="28" t="inlineStr">
-        <is>
-          <t>Recherche Opérationnelle
+      <c r="G58" s="9" t="n"/>
+      <c r="H58" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
 (TD - Salle 30)
-GI S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H58" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 26)
-GI S4 - Groupe: 1</t>
+GI S4 - Groupe: 2</t>
         </is>
       </c>
     </row>
@@ -11416,65 +11402,64 @@
       <c r="H75" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="57">
     <mergeCell ref="B40:B51"/>
-    <mergeCell ref="B22:B27"/>
     <mergeCell ref="A4:A15"/>
+    <mergeCell ref="G4:G15"/>
+    <mergeCell ref="H4:H9"/>
     <mergeCell ref="H16:H27"/>
-    <mergeCell ref="H4:H9"/>
     <mergeCell ref="F52:F63"/>
     <mergeCell ref="F28:F39"/>
-    <mergeCell ref="G8:G11"/>
     <mergeCell ref="B64:B75"/>
     <mergeCell ref="H28:H39"/>
-    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="D64:D75"/>
     <mergeCell ref="B4:B15"/>
-    <mergeCell ref="D64:D75"/>
+    <mergeCell ref="E20:E23"/>
     <mergeCell ref="F64:F75"/>
     <mergeCell ref="A28:A39"/>
+    <mergeCell ref="G16:G27"/>
     <mergeCell ref="H10:H15"/>
-    <mergeCell ref="C28:C39"/>
-    <mergeCell ref="G52:G57"/>
+    <mergeCell ref="B16:B27"/>
+    <mergeCell ref="E52:E57"/>
+    <mergeCell ref="E58:E63"/>
     <mergeCell ref="G40:G51"/>
     <mergeCell ref="A40:A51"/>
-    <mergeCell ref="E16:E27"/>
     <mergeCell ref="A52:A63"/>
     <mergeCell ref="H58:H63"/>
-    <mergeCell ref="E52:E63"/>
+    <mergeCell ref="G52:G63"/>
     <mergeCell ref="A64:A75"/>
     <mergeCell ref="C64:C75"/>
     <mergeCell ref="E64:E75"/>
-    <mergeCell ref="G34:G39"/>
+    <mergeCell ref="H46:H51"/>
+    <mergeCell ref="H40:H45"/>
     <mergeCell ref="F4:F15"/>
-    <mergeCell ref="G28:G33"/>
-    <mergeCell ref="E46:E51"/>
     <mergeCell ref="D40:D51"/>
     <mergeCell ref="F40:F51"/>
     <mergeCell ref="H52:H57"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E40:E45"/>
     <mergeCell ref="C4:C15"/>
     <mergeCell ref="F16:F27"/>
     <mergeCell ref="E4:E15"/>
     <mergeCell ref="B52:B63"/>
     <mergeCell ref="D52:D63"/>
-    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="C36:C39"/>
     <mergeCell ref="H64:H75"/>
+    <mergeCell ref="E16:E19"/>
     <mergeCell ref="C16:C27"/>
-    <mergeCell ref="G58:G63"/>
     <mergeCell ref="E28:E39"/>
-    <mergeCell ref="H40:H51"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="G28:G39"/>
+    <mergeCell ref="C28:C31"/>
     <mergeCell ref="A16:A27"/>
     <mergeCell ref="C40:C51"/>
+    <mergeCell ref="E40:E51"/>
     <mergeCell ref="D4:D15"/>
     <mergeCell ref="C52:C63"/>
     <mergeCell ref="D16:D27"/>
     <mergeCell ref="G64:G75"/>
-    <mergeCell ref="G12:G15"/>
-    <mergeCell ref="G16:G21"/>
     <mergeCell ref="B28:B39"/>
     <mergeCell ref="D28:D39"/>
-    <mergeCell ref="G22:G27"/>
+    <mergeCell ref="E24:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11539,37 +11524,19 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(CM - Amphi 3)
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(CM - Amphi 2)
 Section: GP S4</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
-(TD - Salle 30)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="21" t="n"/>
       <c r="F4" s="20" t="n"/>
-      <c r="G4" s="24" t="inlineStr">
-        <is>
-          <t>Analyse 4
-(CM - Amphi 4)
-Section: GP S4</t>
-        </is>
-      </c>
-      <c r="H4" s="29" t="inlineStr">
-        <is>
-          <t>Analyse Numérique
-(TD - Salle 26)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n"/>
@@ -11687,24 +11654,18 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>Optique Physique
-(CM - Amphi 4)
-Section: GP S4</t>
-        </is>
-      </c>
+      <c r="B16" s="21" t="n"/>
       <c r="C16" s="21" t="n"/>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="21" t="n"/>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>Analyse 4
+(TD - Salle 23)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(TD - Salle 30)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="G16" s="21" t="n"/>
       <c r="H16" s="21" t="n"/>
     </row>
     <row r="17">
@@ -11823,19 +11784,31 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Analyse 4
+(CM - Amphi 3)
+Section: GP S4</t>
+        </is>
+      </c>
       <c r="C28" s="21" t="n"/>
       <c r="D28" s="20" t="n"/>
-      <c r="E28" s="24" t="inlineStr">
-        <is>
-          <t>Analyse 4
-(TD - Salle 23)
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
+(TD - Salle 26)
 GP S4 - Groupe: 1</t>
         </is>
       </c>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="21" t="n"/>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>LTC2 Français
+(TD - Salle 29)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="n"/>
@@ -11953,34 +11926,34 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Développement Personnel
 (CM - Amphi 1)
 Section: GP S4</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Mécanique des Fluides et Transfert Thermique
-(CM - Amphi 4)
+(CM - Amphi 1)
 Section: GP S4</t>
         </is>
       </c>
       <c r="D40" s="20" t="n"/>
       <c r="E40" s="21" t="n"/>
       <c r="F40" s="20" t="n"/>
-      <c r="G40" s="19" t="inlineStr">
-        <is>
-          <t>Structure des Données
-(CM - Amphi 2)
-Section: GP S4</t>
-        </is>
-      </c>
-      <c r="H40" s="29" t="inlineStr">
+      <c r="G40" s="27" t="inlineStr">
         <is>
           <t>Optique Physique
-(TD - Salle 24)
+(TD - Salle 26)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
+(TD - Salle 25)
 GP S4 - Groupe: 1</t>
         </is>
       </c>
@@ -12101,31 +12074,43 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="22" t="inlineStr">
-        <is>
-          <t>LTC2 Français
-(TD - Salle 28)
-GP S4 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>Développement Personnel
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>Analyse Numérique
 (CM - Amphi 2)
 Section: GP S4</t>
         </is>
       </c>
+      <c r="C52" s="27" t="inlineStr">
+        <is>
+          <t>Optique Physique
+(CM - Amphi 4)
+Section: GP S4</t>
+        </is>
+      </c>
       <c r="D52" s="20" t="n"/>
-      <c r="E52" s="24" t="inlineStr">
+      <c r="E52" s="19" t="inlineStr">
         <is>
           <t>Mécanique des Fluides et Transfert Thermique
-(TD - Salle 24)
+(TD - Salle 23)
 GP S4 - Groupe: 1</t>
         </is>
       </c>
       <c r="F52" s="20" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="21" t="n"/>
+      <c r="G52" s="19" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(CM - Amphi 3)
+Section: GP S4</t>
+        </is>
+      </c>
+      <c r="H52" s="19" t="inlineStr">
+        <is>
+          <t>Structure des Données
+(TD - Salle 26)
+GP S4 - Groupe: 1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="n"/>
@@ -12476,40 +12461,34 @@
           <t>LUNDI</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(CM - Amphi 1)
+Section: GP-GI S2</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 24)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(CM - Amphi 1)
+Section: GP-GI S2</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t>Analyse 2
-(TD - Salle 29)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 24)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 23)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="24" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 26)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="H4" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(CM - Amphi 1)
+(CM - Amphi 4)
 Section: GP-GI S2</t>
         </is>
       </c>
@@ -12537,7 +12516,13 @@
     <row r="7">
       <c r="A7" s="9" t="n"/>
       <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 26)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
@@ -12547,21 +12532,9 @@
     <row r="8">
       <c r="A8" s="9" t="n"/>
       <c r="B8" s="9" t="n"/>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 29)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n"/>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 26)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n"/>
       <c r="H8" s="9" t="n"/>
@@ -12578,24 +12551,18 @@
     </row>
     <row r="10">
       <c r="A10" s="9" t="n"/>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 25)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
-      <c r="G10" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 25)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="G10" s="9" t="n"/>
       <c r="H10" s="9" t="n"/>
     </row>
     <row r="11">
@@ -12611,21 +12578,9 @@
     <row r="12">
       <c r="A12" s="9" t="n"/>
       <c r="B12" s="9" t="n"/>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 27)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="C12" s="9" t="n"/>
       <c r="D12" s="9" t="n"/>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 24)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n"/>
       <c r="H12" s="9" t="n"/>
@@ -12633,7 +12588,13 @@
     <row r="13">
       <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
@@ -12666,7 +12627,13 @@
           <t>MARDI</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n"/>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>Electricité
+(CM - Amphi 2)
+Section: GP-GI S2</t>
+        </is>
+      </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
           <t>Structure de la matière
@@ -12675,26 +12642,20 @@
         </is>
       </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
+      <c r="E16" s="21" t="n"/>
       <c r="F16" s="20" t="n"/>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 23)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="H16" s="23" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 23)
-GP-GI S2 - Groupe: 1</t>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(CM - Amphi 2)
+Section: GP-GI S2</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 29)
+GP-GI S2 - Groupe: 4</t>
         </is>
       </c>
     </row>
@@ -12723,13 +12684,7 @@
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="9" t="n"/>
-      <c r="E19" s="23" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 24)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
       <c r="H19" s="9" t="n"/>
@@ -12741,20 +12696,8 @@
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="9" t="n"/>
-      <c r="G20" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
-      <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
-(TD - Salle 29)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n"/>
@@ -12771,16 +12714,16 @@
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="n"/>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 27)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
+      <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
       <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 26)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n"/>
@@ -12799,33 +12742,15 @@
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
-      <c r="G24" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 24)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 30)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="9" t="n"/>
-      <c r="E25" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 25)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
@@ -12856,34 +12781,40 @@
           <t>MERCREDI</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 26)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t>Electricité
-(TD - Salle 24)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(CM - Amphi 2)
-Section: GP-GI S2</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="21" t="n"/>
+(TD - Salle 25)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="F28" s="20" t="n"/>
-      <c r="G28" s="24" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>Circuits électriques et électronique
-(TD - Salle 25)
-GP-GI S2 - Groupe: 5</t>
-        </is>
-      </c>
-      <c r="H28" s="24" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 28)
+(TD - Salle 29)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 27)
 GP-GI S2 - Groupe: 6</t>
         </is>
       </c>
@@ -12915,13 +12846,7 @@
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="9" t="n"/>
-      <c r="G31" s="24" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 26)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="G31" s="9" t="n"/>
       <c r="H31" s="9" t="n"/>
     </row>
     <row r="32">
@@ -12929,10 +12854,22 @@
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="9" t="n"/>
       <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
+      <c r="E32" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 24)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="F32" s="9" t="n"/>
       <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="n"/>
@@ -12946,25 +12883,19 @@
     </row>
     <row r="34">
       <c r="A34" s="9" t="n"/>
-      <c r="B34" s="9" t="n"/>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 28)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
       <c r="C34" s="9" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="9" t="n"/>
-      <c r="G34" s="23" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 24)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="H34" s="23" t="inlineStr">
-        <is>
-          <t>Electricité
-(TD - Salle 24)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n"/>
@@ -12981,10 +12912,22 @@
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="9" t="n"/>
       <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 29)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
       <c r="F36" s="9" t="n"/>
       <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
+      <c r="H36" s="29" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 25)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="n"/>
@@ -12993,13 +12936,7 @@
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="9" t="n"/>
-      <c r="G37" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 30)
-GP-GI S2 - Groupe: 6</t>
-        </is>
-      </c>
+      <c r="G37" s="9" t="n"/>
       <c r="H37" s="9" t="n"/>
     </row>
     <row r="38">
@@ -13028,41 +12965,35 @@
           <t>JEUDI</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
-        <is>
-          <t>Analyse 2
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 25)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (TD - Salle 26)
 GP-GI S2 - Groupe: 5</t>
         </is>
       </c>
-      <c r="C40" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
       <c r="D40" s="20" t="n"/>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(CM - Amphi 2)
-Section: GP-GI S2</t>
-        </is>
-      </c>
+      <c r="E40" s="21" t="n"/>
       <c r="F40" s="20" t="n"/>
-      <c r="G40" s="26" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 28)
+      <c r="G40" s="29" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 29)
 GP-GI S2 - Groupe: 4</t>
         </is>
       </c>
-      <c r="H40" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 28)
-GP-GI S2 - Groupe: 6</t>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 23)
+GP-GI S2 - Groupe: 1</t>
         </is>
       </c>
     </row>
@@ -13078,7 +13009,13 @@
     </row>
     <row r="42">
       <c r="A42" s="9" t="n"/>
-      <c r="B42" s="9" t="n"/>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 29)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="C42" s="9" t="n"/>
       <c r="D42" s="9" t="n"/>
       <c r="E42" s="9" t="n"/>
@@ -13088,14 +13025,14 @@
     </row>
     <row r="43">
       <c r="A43" s="9" t="n"/>
-      <c r="B43" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 24)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 25)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="9" t="n"/>
       <c r="F43" s="9" t="n"/>
@@ -13104,17 +13041,23 @@
     </row>
     <row r="44">
       <c r="A44" s="9" t="n"/>
-      <c r="B44" s="9" t="n"/>
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 24)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="C44" s="9" t="n"/>
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n"/>
-      <c r="H44" s="22" t="inlineStr">
-        <is>
-          <t>Structure de la matière
-(TD - Salle 30)
-GP-GI S2 - Groupe: 3</t>
+      <c r="H44" s="29" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 26)
+GP-GI S2 - Groupe: 5</t>
         </is>
       </c>
     </row>
@@ -13130,14 +13073,20 @@
     </row>
     <row r="46">
       <c r="A46" s="9" t="n"/>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
 (TD - Salle 28)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n"/>
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 29)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="D46" s="9" t="n"/>
       <c r="E46" s="9" t="n"/>
       <c r="F46" s="9" t="n"/>
@@ -13156,30 +13105,36 @@
     </row>
     <row r="48">
       <c r="A48" s="9" t="n"/>
-      <c r="B48" s="9" t="n"/>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Structure de la matière
+(TD - Salle 23)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="C48" s="9" t="n"/>
       <c r="D48" s="9" t="n"/>
       <c r="E48" s="9" t="n"/>
       <c r="F48" s="9" t="n"/>
       <c r="G48" s="9" t="n"/>
-      <c r="H48" s="24" t="inlineStr">
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>Culture digitale
-(TD - Salle 23)
-GP-GI S2 - Groupe: 4</t>
+(TD - Salle 27)
+GP-GI S2 - Groupe: 3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="n"/>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>Culture digitale
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
 (TD - Salle 27)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="n"/>
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D49" s="9" t="n"/>
       <c r="E49" s="9" t="n"/>
       <c r="F49" s="9" t="n"/>
@@ -13212,37 +13167,25 @@
           <t>VENDREDI</t>
         </is>
       </c>
-      <c r="B52" s="26" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Circuits électriques et électronique
+(TD - Salle 25)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
         <is>
           <t>Analyse 2
-(TD - Salle 23)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
-      <c r="C52" s="28" t="inlineStr">
-        <is>
-          <t>Algèbre 2
-(TD - Salle 27)
-GP-GI S2 - Groupe: 2</t>
+(TD - Salle 28)
+GP-GI S2 - Groupe: 3</t>
         </is>
       </c>
       <c r="D52" s="20" t="n"/>
-      <c r="E52" s="23" t="inlineStr">
-        <is>
-          <t>Electricité
-(CM - Amphi 1)
-Section: GP-GI S2</t>
-        </is>
-      </c>
+      <c r="E52" s="21" t="n"/>
       <c r="F52" s="20" t="n"/>
-      <c r="G52" s="26" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(CM - Amphi 2)
-Section: GP-GI S2</t>
-        </is>
-      </c>
-      <c r="H52" s="24" t="inlineStr">
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="18" t="inlineStr">
         <is>
           <t>Circuits électriques et électronique
 (CM - Amphi 2)
@@ -13273,7 +13216,13 @@
     <row r="55">
       <c r="A55" s="9" t="n"/>
       <c r="B55" s="9" t="n"/>
-      <c r="C55" s="9" t="n"/>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>Analyse 2
+(TD - Salle 27)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
       <c r="D55" s="9" t="n"/>
       <c r="E55" s="9" t="n"/>
       <c r="F55" s="9" t="n"/>
@@ -13282,20 +13231,14 @@
     </row>
     <row r="56">
       <c r="A56" s="9" t="n"/>
-      <c r="B56" s="26" t="inlineStr">
-        <is>
-          <t>Analyse 2
-(TD - Salle 29)
-GP-GI S2 - Groupe: 3</t>
-        </is>
-      </c>
-      <c r="C56" s="24" t="inlineStr">
-        <is>
-          <t>Circuits électriques et électronique
-(TD - Salle 25)
-GP-GI S2 - Groupe: 4</t>
-        </is>
-      </c>
+      <c r="B56" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 27)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n"/>
       <c r="D56" s="9" t="n"/>
       <c r="E56" s="9" t="n"/>
       <c r="F56" s="9" t="n"/>
@@ -13315,7 +13258,13 @@
     <row r="58">
       <c r="A58" s="9" t="n"/>
       <c r="B58" s="9" t="n"/>
-      <c r="C58" s="9" t="n"/>
+      <c r="C58" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 25)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
       <c r="D58" s="9" t="n"/>
       <c r="E58" s="9" t="n"/>
       <c r="F58" s="9" t="n"/>
@@ -13334,20 +13283,14 @@
     </row>
     <row r="60">
       <c r="A60" s="9" t="n"/>
-      <c r="B60" s="23" t="inlineStr">
-        <is>
-          <t>Langue Etrangère 2
-(TD - Salle 27)
-GP-GI S2 - Groupe: 2</t>
-        </is>
-      </c>
-      <c r="C60" s="24" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>Culture digitale
-(TD - Salle 24)
-GP-GI S2 - Groupe: 1</t>
-        </is>
-      </c>
+(TD - Salle 29)
+GP-GI S2 - Groupe: 5</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n"/>
       <c r="D60" s="9" t="n"/>
       <c r="E60" s="9" t="n"/>
       <c r="F60" s="9" t="n"/>
@@ -13357,7 +13300,13 @@
     <row r="61">
       <c r="A61" s="9" t="n"/>
       <c r="B61" s="9" t="n"/>
-      <c r="C61" s="9" t="n"/>
+      <c r="C61" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 24)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="D61" s="9" t="n"/>
       <c r="E61" s="9" t="n"/>
       <c r="F61" s="9" t="n"/>
@@ -13390,8 +13339,20 @@
           <t>SAMEDI</t>
         </is>
       </c>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
+      <c r="B64" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 24)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="inlineStr">
+        <is>
+          <t>Algèbre 2
+(TD - Salle 29)
+GP-GI S2 - Groupe: 3</t>
+        </is>
+      </c>
       <c r="D64" s="20" t="n"/>
       <c r="E64" s="21" t="n"/>
       <c r="F64" s="20" t="n"/>
@@ -13430,8 +13391,20 @@
     </row>
     <row r="68">
       <c r="A68" s="9" t="n"/>
-      <c r="B68" s="9" t="n"/>
-      <c r="C68" s="9" t="n"/>
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>Culture digitale
+(TD - Salle 26)
+GP-GI S2 - Groupe: 4</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 25)
+GP-GI S2 - Groupe: 6</t>
+        </is>
+      </c>
       <c r="D68" s="9" t="n"/>
       <c r="E68" s="9" t="n"/>
       <c r="F68" s="9" t="n"/>
@@ -13470,8 +13443,20 @@
     </row>
     <row r="72">
       <c r="A72" s="9" t="n"/>
-      <c r="B72" s="9" t="n"/>
-      <c r="C72" s="9" t="n"/>
+      <c r="B72" s="26" t="inlineStr">
+        <is>
+          <t>Langue Etrangère 2
+(TD - Salle 28)
+GP-GI S2 - Groupe: 1</t>
+        </is>
+      </c>
+      <c r="C72" s="29" t="inlineStr">
+        <is>
+          <t>Electricité
+(TD - Salle 26)
+GP-GI S2 - Groupe: 2</t>
+        </is>
+      </c>
       <c r="D72" s="9" t="n"/>
       <c r="E72" s="9" t="n"/>
       <c r="F72" s="9" t="n"/>
@@ -13509,81 +13494,82 @@
       <c r="H75" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="75">
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="B49:B51"/>
+  <mergeCells count="76">
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="B56:B59"/>
     <mergeCell ref="A4:A15"/>
-    <mergeCell ref="B56:B59"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G4:G15"/>
+    <mergeCell ref="C61:C63"/>
     <mergeCell ref="F52:F63"/>
     <mergeCell ref="F28:F39"/>
-    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="B46:B47"/>
     <mergeCell ref="D64:D75"/>
     <mergeCell ref="F64:F75"/>
     <mergeCell ref="A28:A39"/>
+    <mergeCell ref="G16:G27"/>
     <mergeCell ref="C28:C39"/>
     <mergeCell ref="B16:B27"/>
+    <mergeCell ref="B42:B43"/>
     <mergeCell ref="H44:H47"/>
     <mergeCell ref="G40:G51"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="C13:C15"/>
     <mergeCell ref="H40:H43"/>
-    <mergeCell ref="E4:E7"/>
     <mergeCell ref="B52:B55"/>
+    <mergeCell ref="C7:C9"/>
     <mergeCell ref="A40:A51"/>
+    <mergeCell ref="E16:E27"/>
     <mergeCell ref="A52:A63"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="H34:H39"/>
-    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E52:E63"/>
     <mergeCell ref="H4:H15"/>
-    <mergeCell ref="E52:E63"/>
     <mergeCell ref="G52:G63"/>
     <mergeCell ref="A64:A75"/>
-    <mergeCell ref="C64:C75"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="C56:C59"/>
+    <mergeCell ref="E28:E31"/>
     <mergeCell ref="E64:E75"/>
-    <mergeCell ref="G10:G15"/>
+    <mergeCell ref="H36:H39"/>
     <mergeCell ref="F4:F15"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="B44:B45"/>
     <mergeCell ref="D40:D51"/>
-    <mergeCell ref="G24:G27"/>
+    <mergeCell ref="H32:H35"/>
     <mergeCell ref="F40:F51"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E36:E39"/>
+    <mergeCell ref="C58:C60"/>
     <mergeCell ref="B60:B63"/>
-    <mergeCell ref="C52:C55"/>
     <mergeCell ref="F16:F27"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="E4:E15"/>
+    <mergeCell ref="H22:H27"/>
     <mergeCell ref="D52:D63"/>
-    <mergeCell ref="C60:C63"/>
-    <mergeCell ref="H16:H19"/>
-    <mergeCell ref="G20:G23"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="B68:B71"/>
     <mergeCell ref="H64:H75"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="H16:H21"/>
     <mergeCell ref="C16:C27"/>
-    <mergeCell ref="E28:E39"/>
-    <mergeCell ref="H28:H33"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="G28:G39"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C40:C42"/>
     <mergeCell ref="H52:H63"/>
     <mergeCell ref="A16:A27"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="C40:C51"/>
-    <mergeCell ref="G4:G9"/>
     <mergeCell ref="E40:E51"/>
     <mergeCell ref="D4:D15"/>
     <mergeCell ref="H48:H51"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="G16:G19"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="H24:H27"/>
+    <mergeCell ref="B64:B67"/>
     <mergeCell ref="D16:D27"/>
-    <mergeCell ref="H20:H23"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="C52:C54"/>
     <mergeCell ref="G64:G75"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C68:C71"/>
+    <mergeCell ref="C46:C48"/>
     <mergeCell ref="D28:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
